--- a/Rekap Konsumsi Energi per SPKLU Jawa Barat - Maret 2026.xlsx
+++ b/Rekap Konsumsi Energi per SPKLU Jawa Barat - Maret 2026.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +108,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -475,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J334"/>
+  <dimension ref="A1:L334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -485,9 +488,11 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,15 +547,25 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>Jumlah Transaksi</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Energi Konsumsi Total (kWh)</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Total Pendapatan (Rp)</t>
         </is>
@@ -589,12 +604,18 @@
         </is>
       </c>
       <c r="H4" s="6" t="n">
+        <v>-6.252847</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>107.010401</v>
+      </c>
+      <c r="J4" s="7" t="n">
         <v>5564</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="K4" s="8" t="n">
         <v>129897.15</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="L4" s="7" t="n">
         <v>346064859</v>
       </c>
     </row>
@@ -631,12 +652,18 @@
         </is>
       </c>
       <c r="H5" s="6" t="n">
+        <v>-6.575403</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>106.838482</v>
+      </c>
+      <c r="J5" s="7" t="n">
         <v>3890</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="K5" s="8" t="n">
         <v>93424.49000000001</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="L5" s="7" t="n">
         <v>241978003</v>
       </c>
     </row>
@@ -673,12 +700,18 @@
         </is>
       </c>
       <c r="H6" s="6" t="n">
+        <v>-6.3789</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>106.7457</v>
+      </c>
+      <c r="J6" s="7" t="n">
         <v>2962</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="K6" s="8" t="n">
         <v>70853.12</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="L6" s="7" t="n">
         <v>181767193</v>
       </c>
     </row>
@@ -715,12 +748,18 @@
         </is>
       </c>
       <c r="H7" s="6" t="n">
+        <v>-6.432733</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>106.8261504</v>
+      </c>
+      <c r="J7" s="7" t="n">
         <v>2346</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="K7" s="8" t="n">
         <v>56529.21</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="L7" s="7" t="n">
         <v>145023978</v>
       </c>
     </row>
@@ -757,12 +796,18 @@
         </is>
       </c>
       <c r="H8" s="6" t="n">
+        <v>-6.601573</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>107.4271446</v>
+      </c>
+      <c r="J8" s="7" t="n">
         <v>2192</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="K8" s="8" t="n">
         <v>50637.49</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="L8" s="7" t="n">
         <v>128658443</v>
       </c>
     </row>
@@ -799,12 +844,18 @@
         </is>
       </c>
       <c r="H9" s="6" t="n">
+        <v>-6.5721287</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>106.808797</v>
+      </c>
+      <c r="J9" s="7" t="n">
         <v>1625</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="K9" s="8" t="n">
         <v>47191.93</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="L9" s="7" t="n">
         <v>122233523</v>
       </c>
     </row>
@@ -841,12 +892,18 @@
         </is>
       </c>
       <c r="H10" s="6" t="n">
+        <v>-6.526736</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>106.832144</v>
+      </c>
+      <c r="J10" s="7" t="n">
         <v>1908</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="K10" s="8" t="n">
         <v>45310.82</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="L10" s="7" t="n">
         <v>117359994</v>
       </c>
     </row>
@@ -883,12 +940,18 @@
         </is>
       </c>
       <c r="H11" s="6" t="n">
+        <v>-6.567082</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>106.850909</v>
+      </c>
+      <c r="J11" s="7" t="n">
         <v>1796</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="K11" s="8" t="n">
         <v>43470.77</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="L11" s="7" t="n">
         <v>112595374</v>
       </c>
     </row>
@@ -925,12 +988,18 @@
         </is>
       </c>
       <c r="H12" s="6" t="n">
+        <v>-6.948859</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>107.611765</v>
+      </c>
+      <c r="J12" s="7" t="n">
         <v>1606</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="K12" s="8" t="n">
         <v>43413.79</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="L12" s="7" t="n">
         <v>115660422</v>
       </c>
     </row>
@@ -967,12 +1036,18 @@
         </is>
       </c>
       <c r="H13" s="6" t="n">
+        <v>-6.367146</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>107.360867</v>
+      </c>
+      <c r="J13" s="7" t="n">
         <v>1811</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="K13" s="8" t="n">
         <v>41264.46</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="L13" s="7" t="n">
         <v>105861762</v>
       </c>
     </row>
@@ -1009,12 +1084,18 @@
         </is>
       </c>
       <c r="H14" s="6" t="n">
+        <v>-6.948859</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>107.611765</v>
+      </c>
+      <c r="J14" s="7" t="n">
         <v>1528</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="K14" s="8" t="n">
         <v>39845.05</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="L14" s="7" t="n">
         <v>106153056</v>
       </c>
     </row>
@@ -1051,12 +1132,18 @@
         </is>
       </c>
       <c r="H15" s="6" t="n">
+        <v>-6.9200825</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>107.6093717</v>
+      </c>
+      <c r="J15" s="7" t="n">
         <v>1470</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="K15" s="8" t="n">
         <v>37334.88</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="L15" s="7" t="n">
         <v>99463566</v>
       </c>
     </row>
@@ -1093,12 +1180,18 @@
         </is>
       </c>
       <c r="H16" s="6" t="n">
+        <v>-6.898728</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>107.621305</v>
+      </c>
+      <c r="J16" s="7" t="n">
         <v>1463</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="K16" s="8" t="n">
         <v>36935.94</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="L16" s="7" t="n">
         <v>98402523</v>
       </c>
     </row>
@@ -1135,12 +1228,18 @@
         </is>
       </c>
       <c r="H17" s="6" t="n">
+        <v>-6.239109</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>106.993489</v>
+      </c>
+      <c r="J17" s="7" t="n">
         <v>1512</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="K17" s="8" t="n">
         <v>35427.55</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="L17" s="7" t="n">
         <v>94383885</v>
       </c>
     </row>
@@ -1177,12 +1276,18 @@
         </is>
       </c>
       <c r="H18" s="6" t="n">
+        <v>-6.2584853</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>106.987473</v>
+      </c>
+      <c r="J18" s="7" t="n">
         <v>1456</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="K18" s="8" t="n">
         <v>34638.12</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="L18" s="7" t="n">
         <v>92279982</v>
       </c>
     </row>
@@ -1219,12 +1324,18 @@
         </is>
       </c>
       <c r="H19" s="6" t="n">
+        <v>-6.6042097</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>107.4235304</v>
+      </c>
+      <c r="J19" s="7" t="n">
         <v>1622</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="K19" s="8" t="n">
         <v>34405.62</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="L19" s="7" t="n">
         <v>87417272</v>
       </c>
     </row>
@@ -1261,12 +1372,18 @@
         </is>
       </c>
       <c r="H20" s="6" t="n">
+        <v>-6.596175</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>106.790009</v>
+      </c>
+      <c r="J20" s="7" t="n">
         <v>1392</v>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="K20" s="8" t="n">
         <v>32677.89</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="L20" s="7" t="n">
         <v>84640516</v>
       </c>
     </row>
@@ -1303,12 +1420,18 @@
         </is>
       </c>
       <c r="H21" s="6" t="n">
+        <v>-6.575953</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>106.807518</v>
+      </c>
+      <c r="J21" s="7" t="n">
         <v>1249</v>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="K21" s="8" t="n">
         <v>32059.48</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="L21" s="7" t="n">
         <v>83036501</v>
       </c>
     </row>
@@ -1345,12 +1468,18 @@
         </is>
       </c>
       <c r="H22" s="6" t="n">
+        <v>-6.878957</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>107.597197</v>
+      </c>
+      <c r="J22" s="7" t="n">
         <v>1137</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="K22" s="8" t="n">
         <v>31927.07</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="L22" s="7" t="n">
         <v>83483043</v>
       </c>
     </row>
@@ -1387,12 +1516,18 @@
         </is>
       </c>
       <c r="H23" s="6" t="n">
+        <v>-6.712876</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>108.242674</v>
+      </c>
+      <c r="J23" s="7" t="n">
         <v>1176</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="K23" s="8" t="n">
         <v>31515.55</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="L23" s="7" t="n">
         <v>77742314</v>
       </c>
     </row>
@@ -1429,12 +1564,18 @@
         </is>
       </c>
       <c r="H24" s="6" t="n">
+        <v>-6.71115</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>108.540256</v>
+      </c>
+      <c r="J24" s="7" t="n">
         <v>1104</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="K24" s="8" t="n">
         <v>31455.39</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="L24" s="7" t="n">
         <v>81472135</v>
       </c>
     </row>
@@ -1471,12 +1612,18 @@
         </is>
       </c>
       <c r="H25" s="6" t="n">
+        <v>-6.3886543</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>107.3949849</v>
+      </c>
+      <c r="J25" s="7" t="n">
         <v>1444</v>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="K25" s="8" t="n">
         <v>30922.1</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="L25" s="7" t="n">
         <v>79328518</v>
       </c>
     </row>
@@ -1513,12 +1660,18 @@
         </is>
       </c>
       <c r="H26" s="6" t="n">
+        <v>-6.403602</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>106.83337</v>
+      </c>
+      <c r="J26" s="7" t="n">
         <v>1389</v>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="K26" s="8" t="n">
         <v>30549.34</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="L26" s="7" t="n">
         <v>78371712</v>
       </c>
     </row>
@@ -1555,12 +1708,18 @@
         </is>
       </c>
       <c r="H27" s="6" t="n">
+        <v>-6.706957</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>108.2247718</v>
+      </c>
+      <c r="J27" s="7" t="n">
         <v>1121</v>
       </c>
-      <c r="I27" s="7" t="n">
+      <c r="K27" s="8" t="n">
         <v>28927.91</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="L27" s="7" t="n">
         <v>71358930</v>
       </c>
     </row>
@@ -1597,12 +1756,18 @@
         </is>
       </c>
       <c r="H28" s="6" t="n">
+        <v>-6.898728</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>107.621305</v>
+      </c>
+      <c r="J28" s="7" t="n">
         <v>1371</v>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="K28" s="8" t="n">
         <v>28221.04</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="L28" s="7" t="n">
         <v>75184946</v>
       </c>
     </row>
@@ -1639,12 +1804,18 @@
         </is>
       </c>
       <c r="H29" s="6" t="n">
+        <v>-6.898728</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>107.621305</v>
+      </c>
+      <c r="J29" s="7" t="n">
         <v>1004</v>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="K29" s="8" t="n">
         <v>27872.1</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="L29" s="7" t="n">
         <v>74255216</v>
       </c>
     </row>
@@ -1681,12 +1852,18 @@
         </is>
       </c>
       <c r="H30" s="6" t="n">
+        <v>-6.560036</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>106.788375</v>
+      </c>
+      <c r="J30" s="7" t="n">
         <v>1250</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="K30" s="8" t="n">
         <v>27437.8</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="L30" s="7" t="n">
         <v>71066622</v>
       </c>
     </row>
@@ -1723,12 +1900,18 @@
         </is>
       </c>
       <c r="H31" s="6" t="n">
+        <v>-6.884592</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>108.708023</v>
+      </c>
+      <c r="J31" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="K31" s="8" t="n">
         <v>27405.81</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="L31" s="7" t="n">
         <v>73011830</v>
       </c>
     </row>
@@ -1765,12 +1948,18 @@
         </is>
       </c>
       <c r="H32" s="6" t="n">
+        <v>-6.3915989</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>106.9529614</v>
+      </c>
+      <c r="J32" s="7" t="n">
         <v>1069</v>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="K32" s="8" t="n">
         <v>27127.04</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="L32" s="7" t="n">
         <v>70261735</v>
       </c>
     </row>
@@ -1807,12 +1996,18 @@
         </is>
       </c>
       <c r="H33" s="6" t="n">
+        <v>-6.436056</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>106.851302</v>
+      </c>
+      <c r="J33" s="7" t="n">
         <v>1206</v>
       </c>
-      <c r="I33" s="7" t="n">
+      <c r="K33" s="8" t="n">
         <v>26641.53</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="L33" s="7" t="n">
         <v>68346233</v>
       </c>
     </row>
@@ -1849,12 +2044,18 @@
         </is>
       </c>
       <c r="H34" s="6" t="n">
+        <v>-6.271176</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>107.039319</v>
+      </c>
+      <c r="J34" s="7" t="n">
         <v>1231</v>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="K34" s="8" t="n">
         <v>26496.01</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="L34" s="7" t="n">
         <v>68628063</v>
       </c>
     </row>
@@ -1891,12 +2092,18 @@
         </is>
       </c>
       <c r="H35" s="6" t="n">
+        <v>-6.263917</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>106.995638</v>
+      </c>
+      <c r="J35" s="7" t="n">
         <v>1107</v>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="K35" s="8" t="n">
         <v>26010.48</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="L35" s="7" t="n">
         <v>69294232</v>
       </c>
     </row>
@@ -1933,12 +2140,18 @@
         </is>
       </c>
       <c r="H36" s="6" t="n">
+        <v>-6.655357</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>106.858832</v>
+      </c>
+      <c r="J36" s="7" t="n">
         <v>1163</v>
       </c>
-      <c r="I36" s="7" t="n">
+      <c r="K36" s="8" t="n">
         <v>25911.77</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="L36" s="7" t="n">
         <v>67113543</v>
       </c>
     </row>
@@ -1975,12 +2188,18 @@
         </is>
       </c>
       <c r="H37" s="6" t="n">
+        <v>-6.2690562</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>107.036151</v>
+      </c>
+      <c r="J37" s="7" t="n">
         <v>1033</v>
       </c>
-      <c r="I37" s="7" t="n">
+      <c r="K37" s="8" t="n">
         <v>25295.11</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="L37" s="7" t="n">
         <v>65516514</v>
       </c>
     </row>
@@ -2017,12 +2236,18 @@
         </is>
       </c>
       <c r="H38" s="6" t="n">
+        <v>-6.3813243</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>106.8300326</v>
+      </c>
+      <c r="J38" s="7" t="n">
         <v>978</v>
       </c>
-      <c r="I38" s="7" t="n">
+      <c r="K38" s="8" t="n">
         <v>24930.2</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="L38" s="7" t="n">
         <v>63957687</v>
       </c>
     </row>
@@ -2059,12 +2284,18 @@
         </is>
       </c>
       <c r="H39" s="6" t="n">
+        <v>-6.5091024</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>107.7186932</v>
+      </c>
+      <c r="J39" s="7" t="n">
         <v>896</v>
       </c>
-      <c r="I39" s="7" t="n">
+      <c r="K39" s="8" t="n">
         <v>24713.38</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="L39" s="7" t="n">
         <v>67057870</v>
       </c>
     </row>
@@ -2101,12 +2332,18 @@
         </is>
       </c>
       <c r="H40" s="6" t="n">
+        <v>-6.925774</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>107.636134</v>
+      </c>
+      <c r="J40" s="7" t="n">
         <v>968</v>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="K40" s="8" t="n">
         <v>22745.32</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="L40" s="7" t="n">
         <v>60596953</v>
       </c>
     </row>
@@ -2143,12 +2380,18 @@
         </is>
       </c>
       <c r="H41" s="6" t="n">
+        <v>-6.508229</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>107.721088</v>
+      </c>
+      <c r="J41" s="7" t="n">
         <v>925</v>
       </c>
-      <c r="I41" s="7" t="n">
+      <c r="K41" s="8" t="n">
         <v>21653.29</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="L41" s="7" t="n">
         <v>58754940</v>
       </c>
     </row>
@@ -2185,12 +2428,18 @@
         </is>
       </c>
       <c r="H42" s="6" t="n">
+        <v>-6.22557</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>107.00069</v>
+      </c>
+      <c r="J42" s="7" t="n">
         <v>859</v>
       </c>
-      <c r="I42" s="7" t="n">
+      <c r="K42" s="8" t="n">
         <v>19960.82</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="L42" s="7" t="n">
         <v>53177078</v>
       </c>
     </row>
@@ -2227,12 +2476,18 @@
         </is>
       </c>
       <c r="H43" s="6" t="n">
+        <v>-6.885976</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>107.520432</v>
+      </c>
+      <c r="J43" s="7" t="n">
         <v>683</v>
       </c>
-      <c r="I43" s="7" t="n">
+      <c r="K43" s="8" t="n">
         <v>19887</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="L43" s="7" t="n">
         <v>49057213</v>
       </c>
     </row>
@@ -2269,12 +2524,18 @@
         </is>
       </c>
       <c r="H44" s="6" t="n">
+        <v>-6.466612</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>107.444503</v>
+      </c>
+      <c r="J44" s="7" t="n">
         <v>1036</v>
       </c>
-      <c r="I44" s="7" t="n">
+      <c r="K44" s="8" t="n">
         <v>19677.12</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="L44" s="7" t="n">
         <v>49994315</v>
       </c>
     </row>
@@ -2311,12 +2572,18 @@
         </is>
       </c>
       <c r="H45" s="6" t="n">
+        <v>-6.775515</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>108.562221</v>
+      </c>
+      <c r="J45" s="7" t="n">
         <v>807</v>
       </c>
-      <c r="I45" s="7" t="n">
+      <c r="K45" s="8" t="n">
         <v>19324.16</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="L45" s="7" t="n">
         <v>51481843</v>
       </c>
     </row>
@@ -2353,12 +2620,18 @@
         </is>
       </c>
       <c r="H46" s="6" t="n">
+        <v>-6.385731</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>106.937607</v>
+      </c>
+      <c r="J46" s="7" t="n">
         <v>853</v>
       </c>
-      <c r="I46" s="7" t="n">
+      <c r="K46" s="8" t="n">
         <v>18327.53</v>
       </c>
-      <c r="J46" s="6" t="n">
+      <c r="L46" s="7" t="n">
         <v>47469845</v>
       </c>
     </row>
@@ -2395,12 +2668,18 @@
         </is>
       </c>
       <c r="H47" s="6" t="n">
+        <v>-6.223169</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>106.998075</v>
+      </c>
+      <c r="J47" s="7" t="n">
         <v>858</v>
       </c>
-      <c r="I47" s="7" t="n">
+      <c r="K47" s="8" t="n">
         <v>17986.42</v>
       </c>
-      <c r="J47" s="6" t="n">
+      <c r="L47" s="7" t="n">
         <v>47917256</v>
       </c>
     </row>
@@ -2437,12 +2716,18 @@
         </is>
       </c>
       <c r="H48" s="6" t="n">
+        <v>-6.515967</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>106.757028</v>
+      </c>
+      <c r="J48" s="7" t="n">
         <v>771</v>
       </c>
-      <c r="I48" s="7" t="n">
+      <c r="K48" s="8" t="n">
         <v>17087.41</v>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="L48" s="7" t="n">
         <v>44257788</v>
       </c>
     </row>
@@ -2479,12 +2764,18 @@
         </is>
       </c>
       <c r="H49" s="6" t="n">
+        <v>-6.712701</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>107.010887</v>
+      </c>
+      <c r="J49" s="7" t="n">
         <v>638</v>
       </c>
-      <c r="I49" s="7" t="n">
+      <c r="K49" s="8" t="n">
         <v>16678.76</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="L49" s="7" t="n">
         <v>43610545</v>
       </c>
     </row>
@@ -2521,12 +2812,18 @@
         </is>
       </c>
       <c r="H50" s="6" t="n">
+        <v>-6.711136</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>108.540153</v>
+      </c>
+      <c r="J50" s="7" t="n">
         <v>568</v>
       </c>
-      <c r="I50" s="7" t="n">
+      <c r="K50" s="8" t="n">
         <v>16665.38</v>
       </c>
-      <c r="J50" s="6" t="n">
+      <c r="L50" s="7" t="n">
         <v>43165615</v>
       </c>
     </row>
@@ -2563,12 +2860,18 @@
         </is>
       </c>
       <c r="H51" s="6" t="n">
+        <v>-6.252847</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>107.010401</v>
+      </c>
+      <c r="J51" s="7" t="n">
         <v>728</v>
       </c>
-      <c r="I51" s="7" t="n">
+      <c r="K51" s="8" t="n">
         <v>16632.1</v>
       </c>
-      <c r="J51" s="6" t="n">
+      <c r="L51" s="7" t="n">
         <v>44310341</v>
       </c>
     </row>
@@ -2605,12 +2908,18 @@
         </is>
       </c>
       <c r="H52" s="6" t="n">
+        <v>-6.373445</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>106.745508</v>
+      </c>
+      <c r="J52" s="7" t="n">
         <v>721</v>
       </c>
-      <c r="I52" s="7" t="n">
+      <c r="K52" s="8" t="n">
         <v>16589.13</v>
       </c>
-      <c r="J52" s="6" t="n">
+      <c r="L52" s="7" t="n">
         <v>42558960</v>
       </c>
     </row>
@@ -2647,12 +2956,18 @@
         </is>
       </c>
       <c r="H53" s="6" t="n">
+        <v>-6.57588</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>107.960335</v>
+      </c>
+      <c r="J53" s="7" t="n">
         <v>735</v>
       </c>
-      <c r="I53" s="7" t="n">
+      <c r="K53" s="8" t="n">
         <v>15988.88</v>
       </c>
-      <c r="J53" s="6" t="n">
+      <c r="L53" s="7" t="n">
         <v>41806583</v>
       </c>
     </row>
@@ -2689,12 +3004,18 @@
         </is>
       </c>
       <c r="H54" s="6" t="n">
+        <v>-6.407381</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>106.972579</v>
+      </c>
+      <c r="J54" s="7" t="n">
         <v>646</v>
       </c>
-      <c r="I54" s="7" t="n">
+      <c r="K54" s="8" t="n">
         <v>15790.18</v>
       </c>
-      <c r="J54" s="6" t="n">
+      <c r="L54" s="7" t="n">
         <v>40898766</v>
       </c>
     </row>
@@ -2731,12 +3052,18 @@
         </is>
       </c>
       <c r="H55" s="6" t="n">
+        <v>-6.63647</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>106.843786</v>
+      </c>
+      <c r="J55" s="7" t="n">
         <v>818</v>
       </c>
-      <c r="I55" s="7" t="n">
+      <c r="K55" s="8" t="n">
         <v>15757.69</v>
       </c>
-      <c r="J55" s="6" t="n">
+      <c r="L55" s="7" t="n">
         <v>40813702</v>
       </c>
     </row>
@@ -2773,12 +3100,18 @@
         </is>
       </c>
       <c r="H56" s="6" t="n">
+        <v>-6.778025</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>108.567214</v>
+      </c>
+      <c r="J56" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="I56" s="7" t="n">
+      <c r="K56" s="8" t="n">
         <v>15222.18</v>
       </c>
-      <c r="J56" s="6" t="n">
+      <c r="L56" s="7" t="n">
         <v>40553376</v>
       </c>
     </row>
@@ -2815,12 +3148,18 @@
         </is>
       </c>
       <c r="H57" s="6" t="n">
+        <v>-6.650524</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>106.89581</v>
+      </c>
+      <c r="J57" s="7" t="n">
         <v>664</v>
       </c>
-      <c r="I57" s="7" t="n">
+      <c r="K57" s="8" t="n">
         <v>14842.83</v>
       </c>
-      <c r="J57" s="6" t="n">
+      <c r="L57" s="7" t="n">
         <v>38444967</v>
       </c>
     </row>
@@ -2857,12 +3196,18 @@
         </is>
       </c>
       <c r="H58" s="6" t="n">
+        <v>-7.194623</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>107.886342</v>
+      </c>
+      <c r="J58" s="7" t="n">
         <v>554</v>
       </c>
-      <c r="I58" s="7" t="n">
+      <c r="K58" s="8" t="n">
         <v>13792.84</v>
       </c>
-      <c r="J58" s="6" t="n">
+      <c r="L58" s="7" t="n">
         <v>35725222</v>
       </c>
     </row>
@@ -2899,12 +3244,18 @@
         </is>
       </c>
       <c r="H59" s="6" t="n">
+        <v>-6.881308</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>108.70276</v>
+      </c>
+      <c r="J59" s="7" t="n">
         <v>433</v>
       </c>
-      <c r="I59" s="7" t="n">
+      <c r="K59" s="8" t="n">
         <v>13452.54</v>
       </c>
-      <c r="J59" s="6" t="n">
+      <c r="L59" s="7" t="n">
         <v>35839429</v>
       </c>
     </row>
@@ -2941,12 +3292,18 @@
         </is>
       </c>
       <c r="H60" s="6" t="n">
+        <v>-6.968575</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>107.703976</v>
+      </c>
+      <c r="J60" s="7" t="n">
         <v>538</v>
       </c>
-      <c r="I60" s="7" t="n">
+      <c r="K60" s="8" t="n">
         <v>12520.44</v>
       </c>
-      <c r="J60" s="6" t="n">
+      <c r="L60" s="7" t="n">
         <v>33356063</v>
       </c>
     </row>
@@ -2983,12 +3340,18 @@
         </is>
       </c>
       <c r="H61" s="6" t="n">
+        <v>-6.354965</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>107.230412</v>
+      </c>
+      <c r="J61" s="7" t="n">
         <v>543</v>
       </c>
-      <c r="I61" s="7" t="n">
+      <c r="K61" s="8" t="n">
         <v>11998.83</v>
       </c>
-      <c r="J61" s="6" t="n">
+      <c r="L61" s="7" t="n">
         <v>30782475</v>
       </c>
     </row>
@@ -3025,12 +3388,18 @@
         </is>
       </c>
       <c r="H62" s="6" t="n">
+        <v>-6.6751637</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>107.4391856</v>
+      </c>
+      <c r="J62" s="7" t="n">
         <v>489</v>
       </c>
-      <c r="I62" s="7" t="n">
+      <c r="K62" s="8" t="n">
         <v>10621.53</v>
       </c>
-      <c r="J62" s="6" t="n">
+      <c r="L62" s="7" t="n">
         <v>26987128</v>
       </c>
     </row>
@@ -3067,12 +3436,18 @@
         </is>
       </c>
       <c r="H63" s="6" t="n">
+        <v>-6.940122</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>107.625613</v>
+      </c>
+      <c r="J63" s="7" t="n">
         <v>461</v>
       </c>
-      <c r="I63" s="7" t="n">
+      <c r="K63" s="8" t="n">
         <v>10501.92</v>
       </c>
-      <c r="J63" s="6" t="n">
+      <c r="L63" s="7" t="n">
         <v>27978031</v>
       </c>
     </row>
@@ -3109,12 +3484,18 @@
         </is>
       </c>
       <c r="H64" s="6" t="n">
+        <v>-6.899297</v>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>107.641246</v>
+      </c>
+      <c r="J64" s="7" t="n">
         <v>502</v>
       </c>
-      <c r="I64" s="7" t="n">
+      <c r="K64" s="8" t="n">
         <v>10290.39</v>
       </c>
-      <c r="J64" s="6" t="n">
+      <c r="L64" s="7" t="n">
         <v>27414565</v>
       </c>
     </row>
@@ -3151,12 +3532,18 @@
         </is>
       </c>
       <c r="H65" s="6" t="n">
+        <v>-6.96689</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>107.681659</v>
+      </c>
+      <c r="J65" s="7" t="n">
         <v>471</v>
       </c>
-      <c r="I65" s="7" t="n">
+      <c r="K65" s="8" t="n">
         <v>10284.14</v>
       </c>
-      <c r="J65" s="6" t="n">
+      <c r="L65" s="7" t="n">
         <v>27397706</v>
       </c>
     </row>
@@ -3193,12 +3580,18 @@
         </is>
       </c>
       <c r="H66" s="6" t="n">
+        <v>-6.884346</v>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>108.707599</v>
+      </c>
+      <c r="J66" s="7" t="n">
         <v>336</v>
       </c>
-      <c r="I66" s="7" t="n">
+      <c r="K66" s="8" t="n">
         <v>10134.2</v>
       </c>
-      <c r="J66" s="6" t="n">
+      <c r="L66" s="7" t="n">
         <v>26998486</v>
       </c>
     </row>
@@ -3235,12 +3628,18 @@
         </is>
       </c>
       <c r="H67" s="6" t="n">
+        <v>-6.86738</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>107.464925</v>
+      </c>
+      <c r="J67" s="7" t="n">
         <v>489</v>
       </c>
-      <c r="I67" s="7" t="n">
+      <c r="K67" s="8" t="n">
         <v>9857.370000000001</v>
       </c>
-      <c r="J67" s="6" t="n">
+      <c r="L67" s="7" t="n">
         <v>25044861</v>
       </c>
     </row>
@@ -3277,12 +3676,18 @@
         </is>
       </c>
       <c r="H68" s="6" t="n">
+        <v>-6.5766231</v>
+      </c>
+      <c r="I68" s="6" t="n">
+        <v>107.9601265</v>
+      </c>
+      <c r="J68" s="7" t="n">
         <v>489</v>
       </c>
-      <c r="I68" s="7" t="n">
+      <c r="K68" s="8" t="n">
         <v>9821.940000000001</v>
       </c>
-      <c r="J68" s="6" t="n">
+      <c r="L68" s="7" t="n">
         <v>25682408</v>
       </c>
     </row>
@@ -3319,12 +3724,18 @@
         </is>
       </c>
       <c r="H69" s="6" t="n">
+        <v>-6.938495</v>
+      </c>
+      <c r="I69" s="6" t="n">
+        <v>107.675904</v>
+      </c>
+      <c r="J69" s="7" t="n">
         <v>384</v>
       </c>
-      <c r="I69" s="7" t="n">
+      <c r="K69" s="8" t="n">
         <v>9816.4</v>
       </c>
-      <c r="J69" s="6" t="n">
+      <c r="L69" s="7" t="n">
         <v>26152289</v>
       </c>
     </row>
@@ -3361,12 +3772,18 @@
         </is>
       </c>
       <c r="H70" s="6" t="n">
+        <v>-6.8137203</v>
+      </c>
+      <c r="I70" s="6" t="n">
+        <v>107.1368289</v>
+      </c>
+      <c r="J70" s="7" t="n">
         <v>405</v>
       </c>
-      <c r="I70" s="7" t="n">
+      <c r="K70" s="8" t="n">
         <v>9538.41</v>
       </c>
-      <c r="J70" s="6" t="n">
+      <c r="L70" s="7" t="n">
         <v>24940606</v>
       </c>
     </row>
@@ -3403,12 +3820,18 @@
         </is>
       </c>
       <c r="H71" s="6" t="n">
+        <v>-6.33345</v>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>107.136706</v>
+      </c>
+      <c r="J71" s="7" t="n">
         <v>527</v>
       </c>
-      <c r="I71" s="7" t="n">
+      <c r="K71" s="8" t="n">
         <v>9532.09</v>
       </c>
-      <c r="J71" s="6" t="n">
+      <c r="L71" s="7" t="n">
         <v>24689288</v>
       </c>
     </row>
@@ -3445,12 +3868,18 @@
         </is>
       </c>
       <c r="H72" s="6" t="n">
+        <v>-6.917518</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>107.578369</v>
+      </c>
+      <c r="J72" s="7" t="n">
         <v>438</v>
       </c>
-      <c r="I72" s="7" t="n">
+      <c r="K72" s="8" t="n">
         <v>9093.190000000001</v>
       </c>
-      <c r="J72" s="6" t="n">
+      <c r="L72" s="7" t="n">
         <v>24225477</v>
       </c>
     </row>
@@ -3487,12 +3916,18 @@
         </is>
       </c>
       <c r="H73" s="6" t="n">
+        <v>-6.418477</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>106.826865</v>
+      </c>
+      <c r="J73" s="7" t="n">
         <v>592</v>
       </c>
-      <c r="I73" s="7" t="n">
+      <c r="K73" s="8" t="n">
         <v>9010.18</v>
       </c>
-      <c r="J73" s="6" t="n">
+      <c r="L73" s="7" t="n">
         <v>23114747</v>
       </c>
     </row>
@@ -3529,12 +3964,18 @@
         </is>
       </c>
       <c r="H74" s="6" t="n">
+        <v>-6.857299</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>107.490826</v>
+      </c>
+      <c r="J74" s="7" t="n">
         <v>454</v>
       </c>
-      <c r="I74" s="7" t="n">
+      <c r="K74" s="8" t="n">
         <v>8575.9</v>
       </c>
-      <c r="J74" s="6" t="n">
+      <c r="L74" s="7" t="n">
         <v>21789443</v>
       </c>
     </row>
@@ -3571,12 +4012,18 @@
         </is>
       </c>
       <c r="H75" s="6" t="n">
+        <v>-6.347979</v>
+      </c>
+      <c r="I75" s="6" t="n">
+        <v>107.204346</v>
+      </c>
+      <c r="J75" s="7" t="n">
         <v>483</v>
       </c>
-      <c r="I75" s="7" t="n">
+      <c r="K75" s="8" t="n">
         <v>8532.370000000001</v>
       </c>
-      <c r="J75" s="6" t="n">
+      <c r="L75" s="7" t="n">
         <v>22099616</v>
       </c>
     </row>
@@ -3613,12 +4060,18 @@
         </is>
       </c>
       <c r="H76" s="6" t="n">
+        <v>-7.315839</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>108.230734</v>
+      </c>
+      <c r="J76" s="7" t="n">
         <v>350</v>
       </c>
-      <c r="I76" s="7" t="n">
+      <c r="K76" s="8" t="n">
         <v>8278.34</v>
       </c>
-      <c r="J76" s="6" t="n">
+      <c r="L76" s="7" t="n">
         <v>22463050</v>
       </c>
     </row>
@@ -3655,12 +4108,18 @@
         </is>
       </c>
       <c r="H77" s="6" t="n">
+        <v>-6.8790905</v>
+      </c>
+      <c r="I77" s="6" t="n">
+        <v>107.5972058</v>
+      </c>
+      <c r="J77" s="7" t="n">
         <v>466</v>
       </c>
-      <c r="I77" s="7" t="n">
+      <c r="K77" s="8" t="n">
         <v>6785.97</v>
       </c>
-      <c r="J77" s="6" t="n">
+      <c r="L77" s="7" t="n">
         <v>18078115</v>
       </c>
     </row>
@@ -3697,12 +4156,18 @@
         </is>
       </c>
       <c r="H78" s="6" t="n">
+        <v>-6.889389</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>107.566734</v>
+      </c>
+      <c r="J78" s="7" t="n">
         <v>334</v>
       </c>
-      <c r="I78" s="7" t="n">
+      <c r="K78" s="8" t="n">
         <v>6762.35</v>
       </c>
-      <c r="J78" s="6" t="n">
+      <c r="L78" s="7" t="n">
         <v>18015896</v>
       </c>
     </row>
@@ -3739,12 +4204,18 @@
         </is>
       </c>
       <c r="H79" s="6" t="n">
+        <v>-6.948859</v>
+      </c>
+      <c r="I79" s="6" t="n">
+        <v>107.611765</v>
+      </c>
+      <c r="J79" s="7" t="n">
         <v>377</v>
       </c>
-      <c r="I79" s="7" t="n">
+      <c r="K79" s="8" t="n">
         <v>6723.95</v>
       </c>
-      <c r="J79" s="6" t="n">
+      <c r="L79" s="7" t="n">
         <v>17913505</v>
       </c>
     </row>
@@ -3781,12 +4252,18 @@
         </is>
       </c>
       <c r="H80" s="6" t="n">
+        <v>-6.881331</v>
+      </c>
+      <c r="I80" s="6" t="n">
+        <v>108.7027781</v>
+      </c>
+      <c r="J80" s="7" t="n">
         <v>253</v>
       </c>
-      <c r="I80" s="7" t="n">
+      <c r="K80" s="8" t="n">
         <v>6705.23</v>
       </c>
-      <c r="J80" s="6" t="n">
+      <c r="L80" s="7" t="n">
         <v>17863374</v>
       </c>
     </row>
@@ -3823,12 +4300,18 @@
         </is>
       </c>
       <c r="H81" s="6" t="n">
+        <v>-6.870555</v>
+      </c>
+      <c r="I81" s="6" t="n">
+        <v>107.536452</v>
+      </c>
+      <c r="J81" s="7" t="n">
         <v>319</v>
       </c>
-      <c r="I81" s="7" t="n">
+      <c r="K81" s="8" t="n">
         <v>6646.84</v>
       </c>
-      <c r="J81" s="6" t="n">
+      <c r="L81" s="7" t="n">
         <v>16396345</v>
       </c>
     </row>
@@ -3865,12 +4348,18 @@
         </is>
       </c>
       <c r="H82" s="6" t="n">
+        <v>-6.881331</v>
+      </c>
+      <c r="I82" s="6" t="n">
+        <v>108.7027781</v>
+      </c>
+      <c r="J82" s="7" t="n">
         <v>228</v>
       </c>
-      <c r="I82" s="7" t="n">
+      <c r="K82" s="8" t="n">
         <v>6625.85</v>
       </c>
-      <c r="J82" s="6" t="n">
+      <c r="L82" s="7" t="n">
         <v>17651905</v>
       </c>
     </row>
@@ -3907,12 +4396,18 @@
         </is>
       </c>
       <c r="H83" s="6" t="n">
+        <v>-6.856564</v>
+      </c>
+      <c r="I83" s="6" t="n">
+        <v>107.489628</v>
+      </c>
+      <c r="J83" s="7" t="n">
         <v>286</v>
       </c>
-      <c r="I83" s="7" t="n">
+      <c r="K83" s="8" t="n">
         <v>6548.23</v>
       </c>
-      <c r="J83" s="6" t="n">
+      <c r="L83" s="7" t="n">
         <v>16637940</v>
       </c>
     </row>
@@ -3949,12 +4444,18 @@
         </is>
       </c>
       <c r="H84" s="6" t="n">
+        <v>-6.904819</v>
+      </c>
+      <c r="I84" s="6" t="n">
+        <v>107.674011</v>
+      </c>
+      <c r="J84" s="7" t="n">
         <v>257</v>
       </c>
-      <c r="I84" s="7" t="n">
+      <c r="K84" s="8" t="n">
         <v>6507.68</v>
       </c>
-      <c r="J84" s="6" t="n">
+      <c r="L84" s="7" t="n">
         <v>17336854</v>
       </c>
     </row>
@@ -3991,12 +4492,18 @@
         </is>
       </c>
       <c r="H85" s="6" t="n">
+        <v>-6.884346</v>
+      </c>
+      <c r="I85" s="6" t="n">
+        <v>108.707599</v>
+      </c>
+      <c r="J85" s="7" t="n">
         <v>206</v>
       </c>
-      <c r="I85" s="7" t="n">
+      <c r="K85" s="8" t="n">
         <v>6494.1</v>
       </c>
-      <c r="J85" s="6" t="n">
+      <c r="L85" s="7" t="n">
         <v>17300865</v>
       </c>
     </row>
@@ -4033,12 +4540,18 @@
         </is>
       </c>
       <c r="H86" s="6" t="n">
+        <v>-6.471969</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>107.585774</v>
+      </c>
+      <c r="J86" s="7" t="n">
         <v>341</v>
       </c>
-      <c r="I86" s="7" t="n">
+      <c r="K86" s="8" t="n">
         <v>6122.15</v>
       </c>
-      <c r="J86" s="6" t="n">
+      <c r="L86" s="7" t="n">
         <v>16611923</v>
       </c>
     </row>
@@ -4075,12 +4588,18 @@
         </is>
       </c>
       <c r="H87" s="6" t="n">
+        <v>-7.3715348</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>108.5357498</v>
+      </c>
+      <c r="J87" s="7" t="n">
         <v>266</v>
       </c>
-      <c r="I87" s="7" t="n">
+      <c r="K87" s="8" t="n">
         <v>6003.91</v>
       </c>
-      <c r="J87" s="6" t="n">
+      <c r="L87" s="7" t="n">
         <v>15699091</v>
       </c>
     </row>
@@ -4117,12 +4636,18 @@
         </is>
       </c>
       <c r="H88" s="6" t="n">
+        <v>-6.885276</v>
+      </c>
+      <c r="I88" s="6" t="n">
+        <v>107.612741</v>
+      </c>
+      <c r="J88" s="7" t="n">
         <v>298</v>
       </c>
-      <c r="I88" s="7" t="n">
+      <c r="K88" s="8" t="n">
         <v>5933.66</v>
       </c>
-      <c r="J88" s="6" t="n">
+      <c r="L88" s="7" t="n">
         <v>15807727</v>
       </c>
     </row>
@@ -4159,12 +4684,18 @@
         </is>
       </c>
       <c r="H89" s="6" t="n">
+        <v>-6.301599</v>
+      </c>
+      <c r="I89" s="6" t="n">
+        <v>107.304484</v>
+      </c>
+      <c r="J89" s="7" t="n">
         <v>310</v>
       </c>
-      <c r="I89" s="7" t="n">
+      <c r="K89" s="8" t="n">
         <v>5378.48</v>
       </c>
-      <c r="J89" s="6" t="n">
+      <c r="L89" s="7" t="n">
         <v>13798060</v>
       </c>
     </row>
@@ -4201,12 +4732,18 @@
         </is>
       </c>
       <c r="H90" s="6" t="n">
+        <v>-6.92133</v>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>107.77143</v>
+      </c>
+      <c r="J90" s="7" t="n">
         <v>267</v>
       </c>
-      <c r="I90" s="7" t="n">
+      <c r="K90" s="8" t="n">
         <v>5326.1</v>
       </c>
-      <c r="J90" s="6" t="n">
+      <c r="L90" s="7" t="n">
         <v>13926751</v>
       </c>
     </row>
@@ -4243,12 +4780,18 @@
         </is>
       </c>
       <c r="H91" s="6" t="n">
+        <v>-6.35004</v>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>106.961226</v>
+      </c>
+      <c r="J91" s="7" t="n">
         <v>313</v>
       </c>
-      <c r="I91" s="7" t="n">
+      <c r="K91" s="8" t="n">
         <v>5181.61</v>
       </c>
-      <c r="J91" s="6" t="n">
+      <c r="L91" s="7" t="n">
         <v>13420939</v>
       </c>
     </row>
@@ -4285,12 +4828,18 @@
         </is>
       </c>
       <c r="H92" s="6" t="n">
+        <v>-6.71115</v>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>108.540256</v>
+      </c>
+      <c r="J92" s="7" t="n">
         <v>248</v>
       </c>
-      <c r="I92" s="7" t="n">
+      <c r="K92" s="8" t="n">
         <v>5178.41</v>
       </c>
-      <c r="J92" s="6" t="n">
+      <c r="L92" s="7" t="n">
         <v>13412749</v>
       </c>
     </row>
@@ -4327,12 +4876,18 @@
         </is>
       </c>
       <c r="H93" s="6" t="n">
+        <v>-6.467835</v>
+      </c>
+      <c r="I93" s="6" t="n">
+        <v>107.444582</v>
+      </c>
+      <c r="J93" s="7" t="n">
         <v>392</v>
       </c>
-      <c r="I93" s="7" t="n">
+      <c r="K93" s="8" t="n">
         <v>5135.81</v>
       </c>
-      <c r="J93" s="6" t="n">
+      <c r="L93" s="7" t="n">
         <v>13049108</v>
       </c>
     </row>
@@ -4369,12 +4924,18 @@
         </is>
       </c>
       <c r="H94" s="6" t="n">
+        <v>-6.370291</v>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>106.831942</v>
+      </c>
+      <c r="J94" s="7" t="n">
         <v>263</v>
       </c>
-      <c r="I94" s="7" t="n">
+      <c r="K94" s="8" t="n">
         <v>4825.18</v>
       </c>
-      <c r="J94" s="6" t="n">
+      <c r="L94" s="7" t="n">
         <v>12378893</v>
       </c>
     </row>
@@ -4411,12 +4972,18 @@
         </is>
       </c>
       <c r="H95" s="6" t="n">
+        <v>-6.881331</v>
+      </c>
+      <c r="I95" s="6" t="n">
+        <v>108.7027781</v>
+      </c>
+      <c r="J95" s="7" t="n">
         <v>168</v>
       </c>
-      <c r="I95" s="7" t="n">
+      <c r="K95" s="8" t="n">
         <v>4725.06</v>
       </c>
-      <c r="J95" s="6" t="n">
+      <c r="L95" s="7" t="n">
         <v>12588224</v>
       </c>
     </row>
@@ -4453,12 +5020,18 @@
         </is>
       </c>
       <c r="H96" s="6" t="n">
+        <v>-6.323376</v>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>107.33744</v>
+      </c>
+      <c r="J96" s="7" t="n">
         <v>265</v>
       </c>
-      <c r="I96" s="7" t="n">
+      <c r="K96" s="8" t="n">
         <v>4718.6</v>
       </c>
-      <c r="J96" s="6" t="n">
+      <c r="L96" s="7" t="n">
         <v>12105271</v>
       </c>
     </row>
@@ -4495,12 +5068,18 @@
         </is>
       </c>
       <c r="H97" s="6" t="n">
+        <v>-6.327342</v>
+      </c>
+      <c r="I97" s="6" t="n">
+        <v>107.291973</v>
+      </c>
+      <c r="J97" s="7" t="n">
         <v>236</v>
       </c>
-      <c r="I97" s="7" t="n">
+      <c r="K97" s="8" t="n">
         <v>4713.28</v>
       </c>
-      <c r="J97" s="6" t="n">
+      <c r="L97" s="7" t="n">
         <v>12091810</v>
       </c>
     </row>
@@ -4537,12 +5116,18 @@
         </is>
       </c>
       <c r="H98" s="6" t="n">
+        <v>-6.367095</v>
+      </c>
+      <c r="I98" s="6" t="n">
+        <v>106.834342</v>
+      </c>
+      <c r="J98" s="7" t="n">
         <v>210</v>
       </c>
-      <c r="I98" s="7" t="n">
+      <c r="K98" s="8" t="n">
         <v>4453.48</v>
       </c>
-      <c r="J98" s="6" t="n">
+      <c r="L98" s="7" t="n">
         <v>11424910</v>
       </c>
     </row>
@@ -4579,12 +5164,18 @@
         </is>
       </c>
       <c r="H99" s="6" t="n">
+        <v>-6.913789</v>
+      </c>
+      <c r="I99" s="6" t="n">
+        <v>107.609741</v>
+      </c>
+      <c r="J99" s="7" t="n">
         <v>267</v>
       </c>
-      <c r="I99" s="7" t="n">
+      <c r="K99" s="8" t="n">
         <v>4357.94</v>
       </c>
-      <c r="J99" s="6" t="n">
+      <c r="L99" s="7" t="n">
         <v>11610014</v>
       </c>
     </row>
@@ -4621,12 +5212,18 @@
         </is>
       </c>
       <c r="H100" s="6" t="n">
+        <v>-6.9133375</v>
+      </c>
+      <c r="I100" s="6" t="n">
+        <v>106.9326311</v>
+      </c>
+      <c r="J100" s="7" t="n">
         <v>236</v>
       </c>
-      <c r="I100" s="7" t="n">
+      <c r="K100" s="8" t="n">
         <v>4319.26</v>
       </c>
-      <c r="J100" s="6" t="n">
+      <c r="L100" s="7" t="n">
         <v>11187362</v>
       </c>
     </row>
@@ -4663,12 +5260,18 @@
         </is>
       </c>
       <c r="H101" s="6" t="n">
+        <v>-6.901224</v>
+      </c>
+      <c r="I101" s="6" t="n">
+        <v>107.647999</v>
+      </c>
+      <c r="J101" s="7" t="n">
         <v>159</v>
       </c>
-      <c r="I101" s="7" t="n">
+      <c r="K101" s="8" t="n">
         <v>4262.82</v>
       </c>
-      <c r="J101" s="6" t="n">
+      <c r="L101" s="7" t="n">
         <v>11356756</v>
       </c>
     </row>
@@ -4705,12 +5308,18 @@
         </is>
       </c>
       <c r="H102" s="6" t="n">
+        <v>-7.3260673</v>
+      </c>
+      <c r="I102" s="6" t="n">
+        <v>108.3484199</v>
+      </c>
+      <c r="J102" s="7" t="n">
         <v>195</v>
       </c>
-      <c r="I102" s="7" t="n">
+      <c r="K102" s="8" t="n">
         <v>4195.15</v>
       </c>
-      <c r="J102" s="6" t="n">
+      <c r="L102" s="7" t="n">
         <v>11383426</v>
       </c>
     </row>
@@ -4747,12 +5356,18 @@
         </is>
       </c>
       <c r="H103" s="6" t="n">
+        <v>-6.837547</v>
+      </c>
+      <c r="I103" s="6" t="n">
+        <v>107.916642</v>
+      </c>
+      <c r="J103" s="7" t="n">
         <v>168</v>
       </c>
-      <c r="I103" s="7" t="n">
+      <c r="K103" s="8" t="n">
         <v>3896.5</v>
       </c>
-      <c r="J103" s="6" t="n">
+      <c r="L103" s="7" t="n">
         <v>10188445</v>
       </c>
     </row>
@@ -4789,12 +5404,18 @@
         </is>
       </c>
       <c r="H104" s="6" t="n">
+        <v>-7.327411</v>
+      </c>
+      <c r="I104" s="6" t="n">
+        <v>108.222606</v>
+      </c>
+      <c r="J104" s="7" t="n">
         <v>184</v>
       </c>
-      <c r="I104" s="7" t="n">
+      <c r="K104" s="8" t="n">
         <v>3792.34</v>
       </c>
-      <c r="J104" s="6" t="n">
+      <c r="L104" s="7" t="n">
         <v>10290181</v>
       </c>
     </row>
@@ -4831,12 +5452,18 @@
         </is>
       </c>
       <c r="H105" s="6" t="n">
+        <v>-6.1847863</v>
+      </c>
+      <c r="I105" s="6" t="n">
+        <v>107.0388094</v>
+      </c>
+      <c r="J105" s="7" t="n">
         <v>223</v>
       </c>
-      <c r="I105" s="7" t="n">
+      <c r="K105" s="8" t="n">
         <v>3514.43</v>
       </c>
-      <c r="J105" s="6" t="n">
+      <c r="L105" s="7" t="n">
         <v>9102661</v>
       </c>
     </row>
@@ -4873,12 +5500,18 @@
         </is>
       </c>
       <c r="H106" s="6" t="n">
+        <v>-6.938255</v>
+      </c>
+      <c r="I106" s="6" t="n">
+        <v>107.627926</v>
+      </c>
+      <c r="J106" s="7" t="n">
         <v>196</v>
       </c>
-      <c r="I106" s="7" t="n">
+      <c r="K106" s="8" t="n">
         <v>3407.17</v>
       </c>
-      <c r="J106" s="6" t="n">
+      <c r="L106" s="7" t="n">
         <v>9076872</v>
       </c>
     </row>
@@ -4915,12 +5548,18 @@
         </is>
       </c>
       <c r="H107" s="6" t="n">
+        <v>-6.2528476</v>
+      </c>
+      <c r="I107" s="6" t="n">
+        <v>107.0104015</v>
+      </c>
+      <c r="J107" s="7" t="n">
         <v>262</v>
       </c>
-      <c r="I107" s="7" t="n">
+      <c r="K107" s="8" t="n">
         <v>3400.43</v>
       </c>
-      <c r="J107" s="6" t="n">
+      <c r="L107" s="7" t="n">
         <v>9059031</v>
       </c>
     </row>
@@ -4957,12 +5596,18 @@
         </is>
       </c>
       <c r="H108" s="6" t="n">
+        <v>-6.556471</v>
+      </c>
+      <c r="I108" s="6" t="n">
+        <v>107.445107</v>
+      </c>
+      <c r="J108" s="7" t="n">
         <v>185</v>
       </c>
-      <c r="I108" s="7" t="n">
+      <c r="K108" s="8" t="n">
         <v>3386.66</v>
       </c>
-      <c r="J108" s="6" t="n">
+      <c r="L108" s="7" t="n">
         <v>8604676</v>
       </c>
     </row>
@@ -4999,12 +5644,18 @@
         </is>
       </c>
       <c r="H109" s="6" t="n">
+        <v>-6.594914</v>
+      </c>
+      <c r="I109" s="6" t="n">
+        <v>106.794047</v>
+      </c>
+      <c r="J109" s="7" t="n">
         <v>146</v>
       </c>
-      <c r="I109" s="7" t="n">
+      <c r="K109" s="8" t="n">
         <v>3379.48</v>
       </c>
-      <c r="J109" s="6" t="n">
+      <c r="L109" s="7" t="n">
         <v>8753120</v>
       </c>
     </row>
@@ -5041,12 +5692,18 @@
         </is>
       </c>
       <c r="H110" s="6" t="n">
+        <v>-6.884346</v>
+      </c>
+      <c r="I110" s="6" t="n">
+        <v>108.707599</v>
+      </c>
+      <c r="J110" s="7" t="n">
         <v>146</v>
       </c>
-      <c r="I110" s="7" t="n">
+      <c r="K110" s="8" t="n">
         <v>3301.13</v>
       </c>
-      <c r="J110" s="6" t="n">
+      <c r="L110" s="7" t="n">
         <v>8794690</v>
       </c>
     </row>
@@ -5083,12 +5740,18 @@
         </is>
       </c>
       <c r="H111" s="6" t="n">
+        <v>-7.06085</v>
+      </c>
+      <c r="I111" s="6" t="n">
+        <v>108.0858</v>
+      </c>
+      <c r="J111" s="7" t="n">
         <v>168</v>
       </c>
-      <c r="I111" s="7" t="n">
+      <c r="K111" s="8" t="n">
         <v>3241.02</v>
       </c>
-      <c r="J111" s="6" t="n">
+      <c r="L111" s="7" t="n">
         <v>8394666</v>
       </c>
     </row>
@@ -5125,12 +5788,18 @@
         </is>
       </c>
       <c r="H112" s="6" t="n">
+        <v>-6.972809</v>
+      </c>
+      <c r="I112" s="6" t="n">
+        <v>108.4854</v>
+      </c>
+      <c r="J112" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="I112" s="7" t="n">
+      <c r="K112" s="8" t="n">
         <v>3233.94</v>
       </c>
-      <c r="J112" s="6" t="n">
+      <c r="L112" s="7" t="n">
         <v>8535902</v>
       </c>
     </row>
@@ -5167,12 +5836,18 @@
         </is>
       </c>
       <c r="H113" s="6" t="n">
+        <v>-6.407156</v>
+      </c>
+      <c r="I113" s="6" t="n">
+        <v>107.0055</v>
+      </c>
+      <c r="J113" s="7" t="n">
         <v>178</v>
       </c>
-      <c r="I113" s="7" t="n">
+      <c r="K113" s="8" t="n">
         <v>3191.82</v>
       </c>
-      <c r="J113" s="6" t="n">
+      <c r="L113" s="7" t="n">
         <v>8266977</v>
       </c>
     </row>
@@ -5209,12 +5884,18 @@
         </is>
       </c>
       <c r="H114" s="6" t="n">
+        <v>-6.386798</v>
+      </c>
+      <c r="I114" s="6" t="n">
+        <v>106.925725</v>
+      </c>
+      <c r="J114" s="7" t="n">
         <v>162</v>
       </c>
-      <c r="I114" s="7" t="n">
+      <c r="K114" s="8" t="n">
         <v>3140.56</v>
       </c>
-      <c r="J114" s="6" t="n">
+      <c r="L114" s="7" t="n">
         <v>8366791</v>
       </c>
     </row>
@@ -5251,12 +5932,18 @@
         </is>
       </c>
       <c r="H115" s="6" t="n">
+        <v>-7.020494</v>
+      </c>
+      <c r="I115" s="6" t="n">
+        <v>106.543365</v>
+      </c>
+      <c r="J115" s="7" t="n">
         <v>146</v>
       </c>
-      <c r="I115" s="7" t="n">
+      <c r="K115" s="8" t="n">
         <v>3035.95</v>
       </c>
-      <c r="J115" s="6" t="n">
+      <c r="L115" s="7" t="n">
         <v>7938425</v>
       </c>
     </row>
@@ -5293,12 +5980,18 @@
         </is>
       </c>
       <c r="H116" s="6" t="n">
+        <v>-6.412542</v>
+      </c>
+      <c r="I116" s="6" t="n">
+        <v>106.886044</v>
+      </c>
+      <c r="J116" s="7" t="n">
         <v>143</v>
       </c>
-      <c r="I116" s="7" t="n">
+      <c r="K116" s="8" t="n">
         <v>2956.75</v>
       </c>
-      <c r="J116" s="6" t="n">
+      <c r="L116" s="7" t="n">
         <v>7585233</v>
       </c>
     </row>
@@ -5335,12 +6028,18 @@
         </is>
       </c>
       <c r="H117" s="6" t="n">
+        <v>-6.9414455</v>
+      </c>
+      <c r="I117" s="6" t="n">
+        <v>108.4452062</v>
+      </c>
+      <c r="J117" s="7" t="n">
         <v>110</v>
       </c>
-      <c r="I117" s="7" t="n">
+      <c r="K117" s="8" t="n">
         <v>2942.62</v>
       </c>
-      <c r="J117" s="6" t="n">
+      <c r="L117" s="7" t="n">
         <v>7766952</v>
       </c>
     </row>
@@ -5377,12 +6076,18 @@
         </is>
       </c>
       <c r="H118" s="6" t="n">
+        <v>-6.372754</v>
+      </c>
+      <c r="I118" s="6" t="n">
+        <v>106.834456</v>
+      </c>
+      <c r="J118" s="7" t="n">
         <v>202</v>
       </c>
-      <c r="I118" s="7" t="n">
+      <c r="K118" s="8" t="n">
         <v>2796.05</v>
       </c>
-      <c r="J118" s="6" t="n">
+      <c r="L118" s="7" t="n">
         <v>7172780</v>
       </c>
     </row>
@@ -5419,12 +6124,18 @@
         </is>
       </c>
       <c r="H119" s="6" t="n">
+        <v>-6.296124</v>
+      </c>
+      <c r="I119" s="6" t="n">
+        <v>107.293541</v>
+      </c>
+      <c r="J119" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="I119" s="7" t="n">
+      <c r="K119" s="8" t="n">
         <v>2436.47</v>
       </c>
-      <c r="J119" s="6" t="n">
+      <c r="L119" s="7" t="n">
         <v>6250633</v>
       </c>
     </row>
@@ -5461,12 +6172,18 @@
         </is>
       </c>
       <c r="H120" s="6" t="n">
+        <v>-6.380274</v>
+      </c>
+      <c r="I120" s="6" t="n">
+        <v>106.957463</v>
+      </c>
+      <c r="J120" s="7" t="n">
         <v>139</v>
       </c>
-      <c r="I120" s="7" t="n">
+      <c r="K120" s="8" t="n">
         <v>2403.93</v>
       </c>
-      <c r="J120" s="6" t="n">
+      <c r="L120" s="7" t="n">
         <v>6226383</v>
       </c>
     </row>
@@ -5503,12 +6220,18 @@
         </is>
       </c>
       <c r="H121" s="6" t="n">
+        <v>-6.920338</v>
+      </c>
+      <c r="I121" s="6" t="n">
+        <v>106.932118</v>
+      </c>
+      <c r="J121" s="7" t="n">
         <v>145</v>
       </c>
-      <c r="I121" s="7" t="n">
+      <c r="K121" s="8" t="n">
         <v>2379.32</v>
       </c>
-      <c r="J121" s="6" t="n">
+      <c r="L121" s="7" t="n">
         <v>6162685</v>
       </c>
     </row>
@@ -5545,12 +6268,18 @@
         </is>
       </c>
       <c r="H122" s="6" t="n">
+        <v>-6.598081</v>
+      </c>
+      <c r="I122" s="6" t="n">
+        <v>106.809253</v>
+      </c>
+      <c r="J122" s="7" t="n">
         <v>171</v>
       </c>
-      <c r="I122" s="7" t="n">
+      <c r="K122" s="8" t="n">
         <v>2233.78</v>
       </c>
-      <c r="J122" s="6" t="n">
+      <c r="L122" s="7" t="n">
         <v>5785691</v>
       </c>
     </row>
@@ -5587,12 +6316,18 @@
         </is>
       </c>
       <c r="H123" s="6" t="n">
+        <v>-6.5721287</v>
+      </c>
+      <c r="I123" s="6" t="n">
+        <v>106.808797</v>
+      </c>
+      <c r="J123" s="7" t="n">
         <v>280</v>
       </c>
-      <c r="I123" s="7" t="n">
+      <c r="K123" s="8" t="n">
         <v>2168.8</v>
       </c>
-      <c r="J123" s="6" t="n">
+      <c r="L123" s="7" t="n">
         <v>5617321</v>
       </c>
     </row>
@@ -5629,12 +6364,18 @@
         </is>
       </c>
       <c r="H124" s="6" t="n">
+        <v>-6.283439</v>
+      </c>
+      <c r="I124" s="6" t="n">
+        <v>107.168389</v>
+      </c>
+      <c r="J124" s="7" t="n">
         <v>153</v>
       </c>
-      <c r="I124" s="7" t="n">
+      <c r="K124" s="8" t="n">
         <v>2137.13</v>
       </c>
-      <c r="J124" s="6" t="n">
+      <c r="L124" s="7" t="n">
         <v>5535393</v>
       </c>
     </row>
@@ -5671,12 +6412,18 @@
         </is>
       </c>
       <c r="H125" s="6" t="n">
+        <v>-6.3259718</v>
+      </c>
+      <c r="I125" s="6" t="n">
+        <v>108.3223703</v>
+      </c>
+      <c r="J125" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="I125" s="7" t="n">
+      <c r="K125" s="8" t="n">
         <v>2061.07</v>
       </c>
-      <c r="J125" s="6" t="n">
+      <c r="L125" s="7" t="n">
         <v>5389199</v>
       </c>
     </row>
@@ -5713,12 +6460,18 @@
         </is>
       </c>
       <c r="H126" s="6" t="n">
+        <v>-6.395795</v>
+      </c>
+      <c r="I126" s="6" t="n">
+        <v>106.836799</v>
+      </c>
+      <c r="J126" s="7" t="n">
         <v>186</v>
       </c>
-      <c r="I126" s="7" t="n">
+      <c r="K126" s="8" t="n">
         <v>2016.99</v>
       </c>
-      <c r="J126" s="6" t="n">
+      <c r="L126" s="7" t="n">
         <v>5174417</v>
       </c>
     </row>
@@ -5755,12 +6508,18 @@
         </is>
       </c>
       <c r="H127" s="6" t="n">
+        <v>-6.477392</v>
+      </c>
+      <c r="I127" s="6" t="n">
+        <v>106.803697</v>
+      </c>
+      <c r="J127" s="7" t="n">
         <v>128</v>
       </c>
-      <c r="I127" s="7" t="n">
+      <c r="K127" s="8" t="n">
         <v>1922.79</v>
       </c>
-      <c r="J127" s="6" t="n">
+      <c r="L127" s="7" t="n">
         <v>4980127</v>
       </c>
     </row>
@@ -5796,13 +6555,15 @@
           <t>KAB. SUMEDANG</t>
         </is>
       </c>
-      <c r="H128" s="6" t="n">
+      <c r="H128" s="6" t="inlineStr"/>
+      <c r="I128" s="6" t="inlineStr"/>
+      <c r="J128" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="I128" s="7" t="n">
+      <c r="K128" s="8" t="n">
         <v>1910.39</v>
       </c>
-      <c r="J128" s="6" t="n">
+      <c r="L128" s="7" t="n">
         <v>4995277</v>
       </c>
     </row>
@@ -5839,12 +6600,18 @@
         </is>
       </c>
       <c r="H129" s="6" t="n">
+        <v>-7.684045</v>
+      </c>
+      <c r="I129" s="6" t="n">
+        <v>108.657817</v>
+      </c>
+      <c r="J129" s="7" t="n">
         <v>129</v>
       </c>
-      <c r="I129" s="7" t="n">
+      <c r="K129" s="8" t="n">
         <v>1881.2</v>
       </c>
-      <c r="J129" s="6" t="n">
+      <c r="L129" s="7" t="n">
         <v>5104587</v>
       </c>
     </row>
@@ -5881,12 +6648,18 @@
         </is>
       </c>
       <c r="H130" s="6" t="n">
+        <v>-6.480202</v>
+      </c>
+      <c r="I130" s="6" t="n">
+        <v>106.86465</v>
+      </c>
+      <c r="J130" s="7" t="n">
         <v>139</v>
       </c>
-      <c r="I130" s="7" t="n">
+      <c r="K130" s="8" t="n">
         <v>1871.3</v>
       </c>
-      <c r="J130" s="6" t="n">
+      <c r="L130" s="7" t="n">
         <v>4800601</v>
       </c>
     </row>
@@ -5923,12 +6696,18 @@
         </is>
       </c>
       <c r="H131" s="6" t="n">
+        <v>-6.7138655</v>
+      </c>
+      <c r="I131" s="6" t="n">
+        <v>107.0226114</v>
+      </c>
+      <c r="J131" s="7" t="n">
         <v>161</v>
       </c>
-      <c r="I131" s="7" t="n">
+      <c r="K131" s="8" t="n">
         <v>1853.01</v>
       </c>
-      <c r="J131" s="6" t="n">
+      <c r="L131" s="7" t="n">
         <v>4845149</v>
       </c>
     </row>
@@ -5965,12 +6744,18 @@
         </is>
       </c>
       <c r="H132" s="6" t="n">
+        <v>-7.024873</v>
+      </c>
+      <c r="I132" s="6" t="n">
+        <v>107.528462</v>
+      </c>
+      <c r="J132" s="7" t="n">
         <v>98</v>
       </c>
-      <c r="I132" s="7" t="n">
+      <c r="K132" s="8" t="n">
         <v>1797</v>
       </c>
-      <c r="J132" s="6" t="n">
+      <c r="L132" s="7" t="n">
         <v>4698822</v>
       </c>
     </row>
@@ -6007,12 +6792,18 @@
         </is>
       </c>
       <c r="H133" s="6" t="n">
+        <v>-7.0345837</v>
+      </c>
+      <c r="I133" s="6" t="n">
+        <v>107.9853226</v>
+      </c>
+      <c r="J133" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="I133" s="7" t="n">
+      <c r="K133" s="8" t="n">
         <v>1770.75</v>
       </c>
-      <c r="J133" s="6" t="n">
+      <c r="L133" s="7" t="n">
         <v>4586391</v>
       </c>
     </row>
@@ -6049,12 +6840,18 @@
         </is>
       </c>
       <c r="H134" s="6" t="n">
+        <v>-6.305757</v>
+      </c>
+      <c r="I134" s="6" t="n">
+        <v>107.278373</v>
+      </c>
+      <c r="J134" s="7" t="n">
         <v>88</v>
       </c>
-      <c r="I134" s="7" t="n">
+      <c r="K134" s="8" t="n">
         <v>1750.55</v>
       </c>
-      <c r="J134" s="6" t="n">
+      <c r="L134" s="7" t="n">
         <v>4490881</v>
       </c>
     </row>
@@ -6091,12 +6888,18 @@
         </is>
       </c>
       <c r="H135" s="6" t="n">
+        <v>-6.912297</v>
+      </c>
+      <c r="I135" s="6" t="n">
+        <v>107.597774</v>
+      </c>
+      <c r="J135" s="7" t="n">
         <v>106</v>
       </c>
-      <c r="I135" s="7" t="n">
+      <c r="K135" s="8" t="n">
         <v>1706.08</v>
       </c>
-      <c r="J135" s="6" t="n">
+      <c r="L135" s="7" t="n">
         <v>4545132</v>
       </c>
     </row>
@@ -6133,12 +6936,18 @@
         </is>
       </c>
       <c r="H136" s="6" t="n">
+        <v>-6.411953</v>
+      </c>
+      <c r="I136" s="6" t="n">
+        <v>107.464399</v>
+      </c>
+      <c r="J136" s="7" t="n">
         <v>121</v>
       </c>
-      <c r="I136" s="7" t="n">
+      <c r="K136" s="8" t="n">
         <v>1687.9</v>
       </c>
-      <c r="J136" s="6" t="n">
+      <c r="L136" s="7" t="n">
         <v>4330081</v>
       </c>
     </row>
@@ -6175,12 +6984,18 @@
         </is>
       </c>
       <c r="H137" s="6" t="n">
+        <v>-6.5629531</v>
+      </c>
+      <c r="I137" s="6" t="n">
+        <v>107.7682063</v>
+      </c>
+      <c r="J137" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="I137" s="7" t="n">
+      <c r="K137" s="8" t="n">
         <v>1614.8</v>
       </c>
-      <c r="J137" s="6" t="n">
+      <c r="L137" s="7" t="n">
         <v>4381719</v>
       </c>
     </row>
@@ -6217,12 +7032,18 @@
         </is>
       </c>
       <c r="H138" s="6" t="n">
+        <v>-6.8183273</v>
+      </c>
+      <c r="I138" s="6" t="n">
+        <v>107.6220045</v>
+      </c>
+      <c r="J138" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="I138" s="7" t="n">
+      <c r="K138" s="8" t="n">
         <v>1560.42</v>
       </c>
-      <c r="J138" s="6" t="n">
+      <c r="L138" s="7" t="n">
         <v>3964703</v>
       </c>
     </row>
@@ -6259,12 +7080,18 @@
         </is>
       </c>
       <c r="H139" s="6" t="n">
+        <v>-6.713324</v>
+      </c>
+      <c r="I139" s="6" t="n">
+        <v>108.551606</v>
+      </c>
+      <c r="J139" s="7" t="n">
         <v>102</v>
       </c>
-      <c r="I139" s="7" t="n">
+      <c r="K139" s="8" t="n">
         <v>1545.83</v>
       </c>
-      <c r="J139" s="6" t="n">
+      <c r="L139" s="7" t="n">
         <v>4118229</v>
       </c>
     </row>
@@ -6301,12 +7128,18 @@
         </is>
       </c>
       <c r="H140" s="6" t="n">
+        <v>-6.884346</v>
+      </c>
+      <c r="I140" s="6" t="n">
+        <v>108.707599</v>
+      </c>
+      <c r="J140" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="I140" s="7" t="n">
+      <c r="K140" s="8" t="n">
         <v>1494.14</v>
       </c>
-      <c r="J140" s="6" t="n">
+      <c r="L140" s="7" t="n">
         <v>3980423</v>
       </c>
     </row>
@@ -6343,12 +7176,18 @@
         </is>
       </c>
       <c r="H141" s="6" t="n">
+        <v>-6.509153</v>
+      </c>
+      <c r="I141" s="6" t="n">
+        <v>106.804761</v>
+      </c>
+      <c r="J141" s="7" t="n">
         <v>116</v>
       </c>
-      <c r="I141" s="7" t="n">
+      <c r="K141" s="8" t="n">
         <v>1447.75</v>
       </c>
-      <c r="J141" s="6" t="n">
+      <c r="L141" s="7" t="n">
         <v>3749765</v>
       </c>
     </row>
@@ -6385,12 +7224,18 @@
         </is>
       </c>
       <c r="H142" s="6" t="n">
+        <v>-6.4619294</v>
+      </c>
+      <c r="I142" s="6" t="n">
+        <v>107.0592232</v>
+      </c>
+      <c r="J142" s="7" t="n">
         <v>119</v>
       </c>
-      <c r="I142" s="7" t="n">
+      <c r="K142" s="8" t="n">
         <v>1445.12</v>
       </c>
-      <c r="J142" s="6" t="n">
+      <c r="L142" s="7" t="n">
         <v>3742867</v>
       </c>
     </row>
@@ -6427,12 +7272,18 @@
         </is>
       </c>
       <c r="H143" s="6" t="n">
+        <v>-6.880798</v>
+      </c>
+      <c r="I143" s="6" t="n">
+        <v>108.490502</v>
+      </c>
+      <c r="J143" s="7" t="n">
         <v>71</v>
       </c>
-      <c r="I143" s="7" t="n">
+      <c r="K143" s="8" t="n">
         <v>1438.83</v>
       </c>
-      <c r="J143" s="6" t="n">
+      <c r="L143" s="7" t="n">
         <v>3797749</v>
       </c>
     </row>
@@ -6469,12 +7320,18 @@
         </is>
       </c>
       <c r="H144" s="6" t="n">
+        <v>-6.706957</v>
+      </c>
+      <c r="I144" s="6" t="n">
+        <v>108.2247718</v>
+      </c>
+      <c r="J144" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="I144" s="7" t="n">
+      <c r="K144" s="8" t="n">
         <v>1427.76</v>
       </c>
-      <c r="J144" s="6" t="n">
+      <c r="L144" s="7" t="n">
         <v>3521918</v>
       </c>
     </row>
@@ -6511,12 +7368,18 @@
         </is>
       </c>
       <c r="H145" s="6" t="n">
+        <v>-6.351498</v>
+      </c>
+      <c r="I145" s="6" t="n">
+        <v>106.58071</v>
+      </c>
+      <c r="J145" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="I145" s="7" t="n">
+      <c r="K145" s="8" t="n">
         <v>1417.01</v>
       </c>
-      <c r="J145" s="6" t="n">
+      <c r="L145" s="7" t="n">
         <v>3670266</v>
       </c>
     </row>
@@ -6553,12 +7416,18 @@
         </is>
       </c>
       <c r="H146" s="6" t="n">
+        <v>-6.54272</v>
+      </c>
+      <c r="I146" s="6" t="n">
+        <v>106.812433</v>
+      </c>
+      <c r="J146" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="I146" s="7" t="n">
+      <c r="K146" s="8" t="n">
         <v>1406.99</v>
       </c>
-      <c r="J146" s="6" t="n">
+      <c r="L146" s="7" t="n">
         <v>3644335</v>
       </c>
     </row>
@@ -6595,12 +7464,18 @@
         </is>
       </c>
       <c r="H147" s="6" t="n">
+        <v>-6.763832</v>
+      </c>
+      <c r="I147" s="6" t="n">
+        <v>108.526161</v>
+      </c>
+      <c r="J147" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="I147" s="7" t="n">
+      <c r="K147" s="8" t="n">
         <v>1353.64</v>
       </c>
-      <c r="J147" s="6" t="n">
+      <c r="L147" s="7" t="n">
         <v>3606292</v>
       </c>
     </row>
@@ -6637,12 +7512,18 @@
         </is>
       </c>
       <c r="H148" s="6" t="n">
+        <v>-6.320262</v>
+      </c>
+      <c r="I148" s="6" t="n">
+        <v>107.033516</v>
+      </c>
+      <c r="J148" s="7" t="n">
         <v>152</v>
       </c>
-      <c r="I148" s="7" t="n">
+      <c r="K148" s="8" t="n">
         <v>1332.62</v>
       </c>
-      <c r="J148" s="6" t="n">
+      <c r="L148" s="7" t="n">
         <v>3451563</v>
       </c>
     </row>
@@ -6679,12 +7560,18 @@
         </is>
       </c>
       <c r="H149" s="6" t="n">
+        <v>-6.708359</v>
+      </c>
+      <c r="I149" s="6" t="n">
+        <v>107.022974</v>
+      </c>
+      <c r="J149" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="I149" s="7" t="n">
+      <c r="K149" s="8" t="n">
         <v>1245.91</v>
       </c>
-      <c r="J149" s="6" t="n">
+      <c r="L149" s="7" t="n">
         <v>3257740</v>
       </c>
     </row>
@@ -6721,12 +7608,18 @@
         </is>
       </c>
       <c r="H150" s="6" t="n">
+        <v>-6.266005</v>
+      </c>
+      <c r="I150" s="6" t="n">
+        <v>107.008409</v>
+      </c>
+      <c r="J150" s="7" t="n">
         <v>115</v>
       </c>
-      <c r="I150" s="7" t="n">
+      <c r="K150" s="8" t="n">
         <v>1221.51</v>
       </c>
-      <c r="J150" s="6" t="n">
+      <c r="L150" s="7" t="n">
         <v>3254313</v>
       </c>
     </row>
@@ -6763,12 +7656,18 @@
         </is>
       </c>
       <c r="H151" s="6" t="n">
+        <v>-7.17535</v>
+      </c>
+      <c r="I151" s="6" t="n">
+        <v>107.8864</v>
+      </c>
+      <c r="J151" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="I151" s="7" t="n">
+      <c r="K151" s="8" t="n">
         <v>1213.04</v>
       </c>
-      <c r="J151" s="6" t="n">
+      <c r="L151" s="7" t="n">
         <v>3141945</v>
       </c>
     </row>
@@ -6805,12 +7704,18 @@
         </is>
       </c>
       <c r="H152" s="6" t="n">
+        <v>-6.4122196</v>
+      </c>
+      <c r="I152" s="6" t="n">
+        <v>106.7348817</v>
+      </c>
+      <c r="J152" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="I152" s="7" t="n">
+      <c r="K152" s="8" t="n">
         <v>1201.18</v>
       </c>
-      <c r="J152" s="6" t="n">
+      <c r="L152" s="7" t="n">
         <v>3111108</v>
       </c>
     </row>
@@ -6847,12 +7752,18 @@
         </is>
       </c>
       <c r="H153" s="6" t="n">
+        <v>-7.006074</v>
+      </c>
+      <c r="I153" s="6" t="n">
+        <v>107.62553</v>
+      </c>
+      <c r="J153" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="I153" s="7" t="n">
+      <c r="K153" s="8" t="n">
         <v>1183.5</v>
       </c>
-      <c r="J153" s="6" t="n">
+      <c r="L153" s="7" t="n">
         <v>3094432</v>
       </c>
     </row>
@@ -6889,12 +7800,18 @@
         </is>
       </c>
       <c r="H154" s="6" t="n">
+        <v>-6.246886</v>
+      </c>
+      <c r="I154" s="6" t="n">
+        <v>107.063138</v>
+      </c>
+      <c r="J154" s="7" t="n">
         <v>193</v>
       </c>
-      <c r="I154" s="7" t="n">
+      <c r="K154" s="8" t="n">
         <v>1181.24</v>
       </c>
-      <c r="J154" s="6" t="n">
+      <c r="L154" s="7" t="n">
         <v>3059585</v>
       </c>
     </row>
@@ -6931,12 +7848,18 @@
         </is>
       </c>
       <c r="H155" s="6" t="n">
+        <v>-6.327342</v>
+      </c>
+      <c r="I155" s="6" t="n">
+        <v>107.291973</v>
+      </c>
+      <c r="J155" s="7" t="n">
         <v>116</v>
       </c>
-      <c r="I155" s="7" t="n">
+      <c r="K155" s="8" t="n">
         <v>1158.47</v>
       </c>
-      <c r="J155" s="6" t="n">
+      <c r="L155" s="7" t="n">
         <v>2972059</v>
       </c>
     </row>
@@ -6973,12 +7896,18 @@
         </is>
       </c>
       <c r="H156" s="6" t="n">
+        <v>-6.382608</v>
+      </c>
+      <c r="I156" s="6" t="n">
+        <v>107.040949</v>
+      </c>
+      <c r="J156" s="7" t="n">
         <v>71</v>
       </c>
-      <c r="I156" s="7" t="n">
+      <c r="K156" s="8" t="n">
         <v>1154.21</v>
       </c>
-      <c r="J156" s="6" t="n">
+      <c r="L156" s="7" t="n">
         <v>2989523</v>
       </c>
     </row>
@@ -7015,12 +7944,18 @@
         </is>
       </c>
       <c r="H157" s="6" t="n">
+        <v>-6.380238</v>
+      </c>
+      <c r="I157" s="6" t="n">
+        <v>106.709876</v>
+      </c>
+      <c r="J157" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="I157" s="7" t="n">
+      <c r="K157" s="8" t="n">
         <v>1151.99</v>
       </c>
-      <c r="J157" s="6" t="n">
+      <c r="L157" s="7" t="n">
         <v>2983791</v>
       </c>
     </row>
@@ -7057,12 +7992,18 @@
         </is>
       </c>
       <c r="H158" s="6" t="n">
+        <v>-6.945959</v>
+      </c>
+      <c r="I158" s="6" t="n">
+        <v>107.640992</v>
+      </c>
+      <c r="J158" s="7" t="n">
         <v>93</v>
       </c>
-      <c r="I158" s="7" t="n">
+      <c r="K158" s="8" t="n">
         <v>1120.78</v>
       </c>
-      <c r="J158" s="6" t="n">
+      <c r="L158" s="7" t="n">
         <v>2985948</v>
       </c>
     </row>
@@ -7099,12 +8040,18 @@
         </is>
       </c>
       <c r="H159" s="6" t="n">
+        <v>-7.17829</v>
+      </c>
+      <c r="I159" s="6" t="n">
+        <v>107.8765</v>
+      </c>
+      <c r="J159" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="I159" s="7" t="n">
+      <c r="K159" s="8" t="n">
         <v>1109.27</v>
       </c>
-      <c r="J159" s="6" t="n">
+      <c r="L159" s="7" t="n">
         <v>2873175</v>
       </c>
     </row>
@@ -7120,7 +8067,7 @@
           <t>SPKLU PLN HOTEL ASTON CIREBON</t>
         </is>
       </c>
-      <c r="D160" s="8" t="inlineStr">
+      <c r="D160" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -7141,12 +8088,18 @@
         </is>
       </c>
       <c r="H160" s="6" t="n">
+        <v>-6.7219371</v>
+      </c>
+      <c r="I160" s="6" t="n">
+        <v>108.5392467</v>
+      </c>
+      <c r="J160" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="I160" s="7" t="n">
+      <c r="K160" s="8" t="n">
         <v>1083.46</v>
       </c>
-      <c r="J160" s="6" t="n">
+      <c r="L160" s="7" t="n">
         <v>2806315</v>
       </c>
     </row>
@@ -7183,12 +8136,18 @@
         </is>
       </c>
       <c r="H161" s="6" t="n">
+        <v>-6.89172</v>
+      </c>
+      <c r="I161" s="6" t="n">
+        <v>107.603159</v>
+      </c>
+      <c r="J161" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="I161" s="7" t="n">
+      <c r="K161" s="8" t="n">
         <v>1078.86</v>
       </c>
-      <c r="J161" s="6" t="n">
+      <c r="L161" s="7" t="n">
         <v>2874256</v>
       </c>
     </row>
@@ -7225,12 +8184,18 @@
         </is>
       </c>
       <c r="H162" s="6" t="n">
+        <v>-6.896281</v>
+      </c>
+      <c r="I162" s="6" t="n">
+        <v>106.819305</v>
+      </c>
+      <c r="J162" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="I162" s="7" t="n">
+      <c r="K162" s="8" t="n">
         <v>1073.36</v>
       </c>
-      <c r="J162" s="6" t="n">
+      <c r="L162" s="7" t="n">
         <v>2806528</v>
       </c>
     </row>
@@ -7267,12 +8232,18 @@
         </is>
       </c>
       <c r="H163" s="6" t="n">
+        <v>-6.799632</v>
+      </c>
+      <c r="I163" s="6" t="n">
+        <v>106.775411</v>
+      </c>
+      <c r="J163" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="I163" s="7" t="n">
+      <c r="K163" s="8" t="n">
         <v>1015.87</v>
       </c>
-      <c r="J163" s="6" t="n">
+      <c r="L163" s="7" t="n">
         <v>2656196</v>
       </c>
     </row>
@@ -7309,12 +8280,18 @@
         </is>
       </c>
       <c r="H164" s="6" t="n">
+        <v>-6.71399</v>
+      </c>
+      <c r="I164" s="6" t="n">
+        <v>106.947177</v>
+      </c>
+      <c r="J164" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="I164" s="7" t="n">
+      <c r="K164" s="8" t="n">
         <v>1000.23</v>
       </c>
-      <c r="J164" s="6" t="n">
+      <c r="L164" s="7" t="n">
         <v>2590593</v>
       </c>
     </row>
@@ -7351,12 +8328,18 @@
         </is>
       </c>
       <c r="H165" s="6" t="n">
+        <v>-6.918003</v>
+      </c>
+      <c r="I165" s="6" t="n">
+        <v>106.931326</v>
+      </c>
+      <c r="J165" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="I165" s="7" t="n">
+      <c r="K165" s="8" t="n">
         <v>998.86</v>
       </c>
-      <c r="J165" s="6" t="n">
+      <c r="L165" s="7" t="n">
         <v>2587117</v>
       </c>
     </row>
@@ -7372,7 +8355,7 @@
           <t>SPKLU PLN UID JAWA BARAT</t>
         </is>
       </c>
-      <c r="D166" s="8" t="inlineStr">
+      <c r="D166" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -7393,12 +8376,18 @@
         </is>
       </c>
       <c r="H166" s="6" t="n">
+        <v>-6.920545</v>
+      </c>
+      <c r="I166" s="6" t="n">
+        <v>107.608166</v>
+      </c>
+      <c r="J166" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="I166" s="7" t="n">
+      <c r="K166" s="8" t="n">
         <v>996.34</v>
       </c>
-      <c r="J166" s="6" t="n">
+      <c r="L166" s="7" t="n">
         <v>2654284</v>
       </c>
     </row>
@@ -7435,12 +8424,18 @@
         </is>
       </c>
       <c r="H167" s="6" t="n">
+        <v>-6.830097</v>
+      </c>
+      <c r="I167" s="6" t="n">
+        <v>108.206052</v>
+      </c>
+      <c r="J167" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="I167" s="7" t="n">
+      <c r="K167" s="8" t="n">
         <v>975.48</v>
       </c>
-      <c r="J167" s="6" t="n">
+      <c r="L167" s="7" t="n">
         <v>2406323</v>
       </c>
     </row>
@@ -7477,12 +8472,18 @@
         </is>
       </c>
       <c r="H168" s="6" t="n">
+        <v>-6.3756851</v>
+      </c>
+      <c r="I168" s="6" t="n">
+        <v>106.8635065</v>
+      </c>
+      <c r="J168" s="7" t="n">
         <v>132</v>
       </c>
-      <c r="I168" s="7" t="n">
+      <c r="K168" s="8" t="n">
         <v>941.4400000000001</v>
       </c>
-      <c r="J168" s="6" t="n">
+      <c r="L168" s="7" t="n">
         <v>2415238</v>
       </c>
     </row>
@@ -7519,12 +8520,18 @@
         </is>
       </c>
       <c r="H169" s="6" t="n">
+        <v>-6.2981737</v>
+      </c>
+      <c r="I169" s="6" t="n">
+        <v>107.8208522</v>
+      </c>
+      <c r="J169" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="I169" s="7" t="n">
+      <c r="K169" s="8" t="n">
         <v>939.54</v>
       </c>
-      <c r="J169" s="6" t="n">
+      <c r="L169" s="7" t="n">
         <v>2387169</v>
       </c>
     </row>
@@ -7561,12 +8568,18 @@
         </is>
       </c>
       <c r="H170" s="6" t="n">
+        <v>-6.9115987</v>
+      </c>
+      <c r="I170" s="6" t="n">
+        <v>106.9267196</v>
+      </c>
+      <c r="J170" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="I170" s="7" t="n">
+      <c r="K170" s="8" t="n">
         <v>927.89</v>
       </c>
-      <c r="J170" s="6" t="n">
+      <c r="L170" s="7" t="n">
         <v>2403375</v>
       </c>
     </row>
@@ -7603,12 +8616,18 @@
         </is>
       </c>
       <c r="H171" s="6" t="n">
+        <v>-6.328108</v>
+      </c>
+      <c r="I171" s="6" t="n">
+        <v>107.127747</v>
+      </c>
+      <c r="J171" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="I171" s="7" t="n">
+      <c r="K171" s="8" t="n">
         <v>926.14</v>
       </c>
-      <c r="J171" s="6" t="n">
+      <c r="L171" s="7" t="n">
         <v>2398851</v>
       </c>
     </row>
@@ -7645,12 +8664,18 @@
         </is>
       </c>
       <c r="H172" s="6" t="n">
+        <v>-6.596175</v>
+      </c>
+      <c r="I172" s="6" t="n">
+        <v>106.790009</v>
+      </c>
+      <c r="J172" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="I172" s="7" t="n">
+      <c r="K172" s="8" t="n">
         <v>916.3200000000001</v>
       </c>
-      <c r="J172" s="6" t="n">
+      <c r="L172" s="7" t="n">
         <v>2373193</v>
       </c>
     </row>
@@ -7687,12 +8712,18 @@
         </is>
       </c>
       <c r="H173" s="6" t="n">
+        <v>-6.564198</v>
+      </c>
+      <c r="I173" s="6" t="n">
+        <v>106.677962</v>
+      </c>
+      <c r="J173" s="7" t="n">
         <v>98</v>
       </c>
-      <c r="I173" s="7" t="n">
+      <c r="K173" s="8" t="n">
         <v>905.21</v>
       </c>
-      <c r="J173" s="6" t="n">
+      <c r="L173" s="7" t="n">
         <v>2344529</v>
       </c>
     </row>
@@ -7708,7 +8739,7 @@
           <t>SPKLU PLN HOTEL LE EMINENCE LEMBANG</t>
         </is>
       </c>
-      <c r="D174" s="8" t="inlineStr">
+      <c r="D174" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -7729,12 +8760,18 @@
         </is>
       </c>
       <c r="H174" s="6" t="n">
+        <v>-6.819935</v>
+      </c>
+      <c r="I174" s="6" t="n">
+        <v>107.627782</v>
+      </c>
+      <c r="J174" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="I174" s="7" t="n">
+      <c r="K174" s="8" t="n">
         <v>877.26</v>
       </c>
-      <c r="J174" s="6" t="n">
+      <c r="L174" s="7" t="n">
         <v>2228954</v>
       </c>
     </row>
@@ -7771,12 +8808,18 @@
         </is>
       </c>
       <c r="H175" s="6" t="n">
+        <v>-6.407381</v>
+      </c>
+      <c r="I175" s="6" t="n">
+        <v>106.972579</v>
+      </c>
+      <c r="J175" s="7" t="n">
         <v>97</v>
       </c>
-      <c r="I175" s="7" t="n">
+      <c r="K175" s="8" t="n">
         <v>852.5599999999999</v>
       </c>
-      <c r="J175" s="6" t="n">
+      <c r="L175" s="7" t="n">
         <v>2208030</v>
       </c>
     </row>
@@ -7813,12 +8856,18 @@
         </is>
       </c>
       <c r="H176" s="6" t="n">
+        <v>-6.249609</v>
+      </c>
+      <c r="I176" s="6" t="n">
+        <v>107.016711</v>
+      </c>
+      <c r="J176" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="I176" s="7" t="n">
+      <c r="K176" s="8" t="n">
         <v>848.28</v>
       </c>
-      <c r="J176" s="6" t="n">
+      <c r="L176" s="7" t="n">
         <v>2259712</v>
       </c>
     </row>
@@ -7834,7 +8883,7 @@
           <t>SPKLU PLN PRIMAYA HOSPITAL KARAWANG</t>
         </is>
       </c>
-      <c r="D177" s="8" t="inlineStr">
+      <c r="D177" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -7855,12 +8904,18 @@
         </is>
       </c>
       <c r="H177" s="6" t="n">
+        <v>-6.330123</v>
+      </c>
+      <c r="I177" s="6" t="n">
+        <v>107.297147</v>
+      </c>
+      <c r="J177" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="I177" s="7" t="n">
+      <c r="K177" s="8" t="n">
         <v>846.26</v>
       </c>
-      <c r="J177" s="6" t="n">
+      <c r="L177" s="7" t="n">
         <v>2170999</v>
       </c>
     </row>
@@ -7876,7 +8931,7 @@
           <t>SPKLU Fieris Hotel Kertajati</t>
         </is>
       </c>
-      <c r="D178" s="8" t="inlineStr">
+      <c r="D178" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -7897,12 +8952,18 @@
         </is>
       </c>
       <c r="H178" s="6" t="n">
+        <v>-6.7141582</v>
+      </c>
+      <c r="I178" s="6" t="n">
+        <v>108.1713013</v>
+      </c>
+      <c r="J178" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="I178" s="7" t="n">
+      <c r="K178" s="8" t="n">
         <v>840.64</v>
       </c>
-      <c r="J178" s="6" t="n">
+      <c r="L178" s="7" t="n">
         <v>2073620</v>
       </c>
     </row>
@@ -7918,7 +8979,7 @@
           <t>SPKLU PLN Best Western Hotel Setiabudhi Bandung</t>
         </is>
       </c>
-      <c r="D179" s="8" t="inlineStr">
+      <c r="D179" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -7939,12 +9000,18 @@
         </is>
       </c>
       <c r="H179" s="6" t="n">
+        <v>-6.861207</v>
+      </c>
+      <c r="I179" s="6" t="n">
+        <v>107.595032</v>
+      </c>
+      <c r="J179" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="I179" s="7" t="n">
+      <c r="K179" s="8" t="n">
         <v>825.4400000000001</v>
       </c>
-      <c r="J179" s="6" t="n">
+      <c r="L179" s="7" t="n">
         <v>2198990</v>
       </c>
     </row>
@@ -7960,7 +9027,7 @@
           <t>SPKLU PLN HOTEL GRAND PALMA PANGANDARAN</t>
         </is>
       </c>
-      <c r="D180" s="8" t="inlineStr">
+      <c r="D180" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -7981,12 +9048,18 @@
         </is>
       </c>
       <c r="H180" s="6" t="n">
+        <v>-7.7038749</v>
+      </c>
+      <c r="I180" s="6" t="n">
+        <v>108.6564497</v>
+      </c>
+      <c r="J180" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="I180" s="7" t="n">
+      <c r="K180" s="8" t="n">
         <v>821.47</v>
       </c>
-      <c r="J180" s="6" t="n">
+      <c r="L180" s="7" t="n">
         <v>2228998</v>
       </c>
     </row>
@@ -8002,7 +9075,7 @@
           <t>SPKLU RS SENTOSA</t>
         </is>
       </c>
-      <c r="D181" s="8" t="inlineStr">
+      <c r="D181" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -8023,12 +9096,18 @@
         </is>
       </c>
       <c r="H181" s="6" t="n">
+        <v>-6.4950254</v>
+      </c>
+      <c r="I181" s="6" t="n">
+        <v>106.7512742</v>
+      </c>
+      <c r="J181" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="I181" s="7" t="n">
+      <c r="K181" s="8" t="n">
         <v>793.6900000000001</v>
       </c>
-      <c r="J181" s="6" t="n">
+      <c r="L181" s="7" t="n">
         <v>2055701</v>
       </c>
     </row>
@@ -8065,12 +9144,18 @@
         </is>
       </c>
       <c r="H182" s="6" t="n">
+        <v>-6.7208027</v>
+      </c>
+      <c r="I182" s="6" t="n">
+        <v>108.5501528</v>
+      </c>
+      <c r="J182" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="I182" s="7" t="n">
+      <c r="K182" s="8" t="n">
         <v>787.38</v>
       </c>
-      <c r="J182" s="6" t="n">
+      <c r="L182" s="7" t="n">
         <v>2039442</v>
       </c>
     </row>
@@ -8107,12 +9192,18 @@
         </is>
       </c>
       <c r="H183" s="6" t="n">
+        <v>-6.597243</v>
+      </c>
+      <c r="I183" s="6" t="n">
+        <v>106.890222</v>
+      </c>
+      <c r="J183" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="I183" s="7" t="n">
+      <c r="K183" s="8" t="n">
         <v>780.72</v>
       </c>
-      <c r="J183" s="6" t="n">
+      <c r="L183" s="7" t="n">
         <v>2022037</v>
       </c>
     </row>
@@ -8128,7 +9219,7 @@
           <t>SPKLU PLN ULP SUMEDANG KOTA</t>
         </is>
       </c>
-      <c r="D184" s="8" t="inlineStr">
+      <c r="D184" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -8149,12 +9240,18 @@
         </is>
       </c>
       <c r="H184" s="6" t="n">
+        <v>-6.85681</v>
+      </c>
+      <c r="I184" s="6" t="n">
+        <v>107.920992</v>
+      </c>
+      <c r="J184" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="I184" s="7" t="n">
+      <c r="K184" s="8" t="n">
         <v>768.53</v>
       </c>
-      <c r="J184" s="6" t="n">
+      <c r="L184" s="7" t="n">
         <v>2009564</v>
       </c>
     </row>
@@ -8170,7 +9267,7 @@
           <t>SPKLU PLN MALL INDRAMAYU</t>
         </is>
       </c>
-      <c r="D185" s="8" t="inlineStr">
+      <c r="D185" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -8191,12 +9288,18 @@
         </is>
       </c>
       <c r="H185" s="6" t="n">
+        <v>-6.342445</v>
+      </c>
+      <c r="I185" s="6" t="n">
+        <v>108.334835</v>
+      </c>
+      <c r="J185" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="I185" s="7" t="n">
+      <c r="K185" s="8" t="n">
         <v>761.38</v>
       </c>
-      <c r="J185" s="6" t="n">
+      <c r="L185" s="7" t="n">
         <v>1990734</v>
       </c>
     </row>
@@ -8233,12 +9336,18 @@
         </is>
       </c>
       <c r="H186" s="6" t="n">
+        <v>-6.406121</v>
+      </c>
+      <c r="I186" s="6" t="n">
+        <v>106.984169</v>
+      </c>
+      <c r="J186" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="I186" s="7" t="n">
+      <c r="K186" s="8" t="n">
         <v>757.35</v>
       </c>
-      <c r="J186" s="6" t="n">
+      <c r="L186" s="7" t="n">
         <v>1961566</v>
       </c>
     </row>
@@ -8275,12 +9384,18 @@
         </is>
       </c>
       <c r="H187" s="6" t="n">
+        <v>-6.706646</v>
+      </c>
+      <c r="I187" s="6" t="n">
+        <v>106.993126</v>
+      </c>
+      <c r="J187" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="I187" s="7" t="n">
+      <c r="K187" s="8" t="n">
         <v>751.86</v>
       </c>
-      <c r="J187" s="6" t="n">
+      <c r="L187" s="7" t="n">
         <v>1965977</v>
       </c>
     </row>
@@ -8296,7 +9411,7 @@
           <t>SPKLU PLN ULP SUKARAJA</t>
         </is>
       </c>
-      <c r="D188" s="8" t="inlineStr">
+      <c r="D188" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -8317,12 +9432,18 @@
         </is>
       </c>
       <c r="H188" s="6" t="n">
+        <v>-6.917551</v>
+      </c>
+      <c r="I188" s="6" t="n">
+        <v>106.965165</v>
+      </c>
+      <c r="J188" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="I188" s="7" t="n">
+      <c r="K188" s="8" t="n">
         <v>748.77</v>
       </c>
-      <c r="J188" s="6" t="n">
+      <c r="L188" s="7" t="n">
         <v>1957834</v>
       </c>
     </row>
@@ -8338,7 +9459,7 @@
           <t>SPKLU PLN ULP HAURGEULIS</t>
         </is>
       </c>
-      <c r="D189" s="8" t="inlineStr">
+      <c r="D189" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -8359,12 +9480,18 @@
         </is>
       </c>
       <c r="H189" s="6" t="n">
+        <v>-6.4393054</v>
+      </c>
+      <c r="I189" s="6" t="n">
+        <v>107.9461854</v>
+      </c>
+      <c r="J189" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="I189" s="7" t="n">
+      <c r="K189" s="8" t="n">
         <v>727.85</v>
       </c>
-      <c r="J189" s="6" t="n">
+      <c r="L189" s="7" t="n">
         <v>1903139</v>
       </c>
     </row>
@@ -8401,12 +9528,18 @@
         </is>
       </c>
       <c r="H190" s="6" t="n">
+        <v>-6.327342</v>
+      </c>
+      <c r="I190" s="6" t="n">
+        <v>107.291973</v>
+      </c>
+      <c r="J190" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="I190" s="7" t="n">
+      <c r="K190" s="8" t="n">
         <v>722.21</v>
       </c>
-      <c r="J190" s="6" t="n">
+      <c r="L190" s="7" t="n">
         <v>1852826</v>
       </c>
     </row>
@@ -8443,12 +9576,18 @@
         </is>
       </c>
       <c r="H191" s="6" t="n">
+        <v>-6.715324</v>
+      </c>
+      <c r="I191" s="6" t="n">
+        <v>107.026144</v>
+      </c>
+      <c r="J191" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="I191" s="7" t="n">
+      <c r="K191" s="8" t="n">
         <v>712.49</v>
       </c>
-      <c r="J191" s="6" t="n">
+      <c r="L191" s="7" t="n">
         <v>1862895</v>
       </c>
     </row>
@@ -8485,12 +9624,18 @@
         </is>
       </c>
       <c r="H192" s="6" t="n">
+        <v>-6.3714181</v>
+      </c>
+      <c r="I192" s="6" t="n">
+        <v>107.3788545</v>
+      </c>
+      <c r="J192" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="I192" s="7" t="n">
+      <c r="K192" s="8" t="n">
         <v>698.9</v>
       </c>
-      <c r="J192" s="6" t="n">
+      <c r="L192" s="7" t="n">
         <v>1793027</v>
       </c>
     </row>
@@ -8506,7 +9651,7 @@
           <t>SPKLU PLN ULP PRIMA CIBABAT</t>
         </is>
       </c>
-      <c r="D193" s="8" t="inlineStr">
+      <c r="D193" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -8527,12 +9672,18 @@
         </is>
       </c>
       <c r="H193" s="6" t="n">
+        <v>-6.8757411</v>
+      </c>
+      <c r="I193" s="6" t="n">
+        <v>107.5448649</v>
+      </c>
+      <c r="J193" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="I193" s="7" t="n">
+      <c r="K193" s="8" t="n">
         <v>696.6900000000001</v>
       </c>
-      <c r="J193" s="6" t="n">
+      <c r="L193" s="7" t="n">
         <v>1718612</v>
       </c>
     </row>
@@ -8548,7 +9699,7 @@
           <t>SPKLU PLN Kantor Pemkot Cimahi</t>
         </is>
       </c>
-      <c r="D194" s="8" t="inlineStr">
+      <c r="D194" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -8569,12 +9720,18 @@
         </is>
       </c>
       <c r="H194" s="6" t="n">
+        <v>-6.869667</v>
+      </c>
+      <c r="I194" s="6" t="n">
+        <v>107.555337</v>
+      </c>
+      <c r="J194" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="I194" s="7" t="n">
+      <c r="K194" s="8" t="n">
         <v>685.66</v>
       </c>
-      <c r="J194" s="6" t="n">
+      <c r="L194" s="7" t="n">
         <v>1691314</v>
       </c>
     </row>
@@ -8611,12 +9768,18 @@
         </is>
       </c>
       <c r="H195" s="6" t="n">
+        <v>-6.266739</v>
+      </c>
+      <c r="I195" s="6" t="n">
+        <v>107.130728</v>
+      </c>
+      <c r="J195" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="I195" s="7" t="n">
+      <c r="K195" s="8" t="n">
         <v>682.99</v>
       </c>
-      <c r="J195" s="6" t="n">
+      <c r="L195" s="7" t="n">
         <v>1768918</v>
       </c>
     </row>
@@ -8653,12 +9816,18 @@
         </is>
       </c>
       <c r="H196" s="6" t="n">
+        <v>-6.239109</v>
+      </c>
+      <c r="I196" s="6" t="n">
+        <v>106.993489</v>
+      </c>
+      <c r="J196" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="I196" s="7" t="n">
+      <c r="K196" s="8" t="n">
         <v>677.6799999999999</v>
       </c>
-      <c r="J196" s="6" t="n">
+      <c r="L196" s="7" t="n">
         <v>1805314</v>
       </c>
     </row>
@@ -8695,12 +9864,18 @@
         </is>
       </c>
       <c r="H197" s="6" t="n">
+        <v>-6.59499</v>
+      </c>
+      <c r="I197" s="6" t="n">
+        <v>106.794047</v>
+      </c>
+      <c r="J197" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="I197" s="7" t="n">
+      <c r="K197" s="8" t="n">
         <v>658.08</v>
       </c>
-      <c r="J197" s="6" t="n">
+      <c r="L197" s="7" t="n">
         <v>1704536</v>
       </c>
     </row>
@@ -8737,12 +9912,18 @@
         </is>
       </c>
       <c r="H198" s="6" t="n">
+        <v>-6.908072</v>
+      </c>
+      <c r="I198" s="6" t="n">
+        <v>107.631205</v>
+      </c>
+      <c r="J198" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I198" s="7" t="n">
+      <c r="K198" s="8" t="n">
         <v>656.4400000000001</v>
       </c>
-      <c r="J198" s="6" t="n">
+      <c r="L198" s="7" t="n">
         <v>1716479</v>
       </c>
     </row>
@@ -8779,12 +9960,18 @@
         </is>
       </c>
       <c r="H199" s="6" t="n">
+        <v>-7.020754</v>
+      </c>
+      <c r="I199" s="6" t="n">
+        <v>107.5296088</v>
+      </c>
+      <c r="J199" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="I199" s="7" t="n">
+      <c r="K199" s="8" t="n">
         <v>645.28</v>
       </c>
-      <c r="J199" s="6" t="n">
+      <c r="L199" s="7" t="n">
         <v>1687335</v>
       </c>
     </row>
@@ -8800,7 +9987,7 @@
           <t>SPKLU PLN TEUAN CAFE &amp; RESTO</t>
         </is>
       </c>
-      <c r="D200" s="8" t="inlineStr">
+      <c r="D200" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -8821,12 +10008,18 @@
         </is>
       </c>
       <c r="H200" s="6" t="n">
+        <v>-6.8146673</v>
+      </c>
+      <c r="I200" s="6" t="n">
+        <v>107.6249528</v>
+      </c>
+      <c r="J200" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="I200" s="7" t="n">
+      <c r="K200" s="8" t="n">
         <v>642.76</v>
       </c>
-      <c r="J200" s="6" t="n">
+      <c r="L200" s="7" t="n">
         <v>1633081</v>
       </c>
     </row>
@@ -8842,7 +10035,7 @@
           <t>SPKLU PLN GRAGE LANAI RESTO</t>
         </is>
       </c>
-      <c r="D201" s="8" t="inlineStr">
+      <c r="D201" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -8863,12 +10056,18 @@
         </is>
       </c>
       <c r="H201" s="6" t="n">
+        <v>-6.8864377</v>
+      </c>
+      <c r="I201" s="6" t="n">
+        <v>108.4980474</v>
+      </c>
+      <c r="J201" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="I201" s="7" t="n">
+      <c r="K201" s="8" t="n">
         <v>642.35</v>
       </c>
-      <c r="J201" s="6" t="n">
+      <c r="L201" s="7" t="n">
         <v>1695393</v>
       </c>
     </row>
@@ -8905,12 +10104,18 @@
         </is>
       </c>
       <c r="H202" s="6" t="n">
+        <v>-6.328612</v>
+      </c>
+      <c r="I202" s="6" t="n">
+        <v>107.29332</v>
+      </c>
+      <c r="J202" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="I202" s="7" t="n">
+      <c r="K202" s="8" t="n">
         <v>631.09</v>
       </c>
-      <c r="J202" s="6" t="n">
+      <c r="L202" s="7" t="n">
         <v>1619063</v>
       </c>
     </row>
@@ -8947,12 +10152,18 @@
         </is>
       </c>
       <c r="H203" s="6" t="n">
+        <v>-6.458986</v>
+      </c>
+      <c r="I203" s="6" t="n">
+        <v>106.896763</v>
+      </c>
+      <c r="J203" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I203" s="7" t="n">
+      <c r="K203" s="8" t="n">
         <v>630.99</v>
       </c>
-      <c r="J203" s="6" t="n">
+      <c r="L203" s="7" t="n">
         <v>1634340</v>
       </c>
     </row>
@@ -8968,7 +10179,7 @@
           <t>SPKLU PLN ULP CIJAWURA</t>
         </is>
       </c>
-      <c r="D204" s="8" t="inlineStr">
+      <c r="D204" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -8989,12 +10200,18 @@
         </is>
       </c>
       <c r="H204" s="6" t="n">
+        <v>-6.954136</v>
+      </c>
+      <c r="I204" s="6" t="n">
+        <v>107.640536</v>
+      </c>
+      <c r="J204" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="I204" s="7" t="n">
+      <c r="K204" s="8" t="n">
         <v>628.62</v>
       </c>
-      <c r="J204" s="6" t="n">
+      <c r="L204" s="7" t="n">
         <v>1674668</v>
       </c>
     </row>
@@ -9010,7 +10227,7 @@
           <t>SPKLU Hotel Emaki Jatinangor</t>
         </is>
       </c>
-      <c r="D205" s="8" t="inlineStr">
+      <c r="D205" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9031,12 +10248,18 @@
         </is>
       </c>
       <c r="H205" s="6" t="n">
+        <v>-6.937193</v>
+      </c>
+      <c r="I205" s="6" t="n">
+        <v>107.759218</v>
+      </c>
+      <c r="J205" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="I205" s="7" t="n">
+      <c r="K205" s="8" t="n">
         <v>621.58</v>
       </c>
-      <c r="J205" s="6" t="n">
+      <c r="L205" s="7" t="n">
         <v>1625317</v>
       </c>
     </row>
@@ -9052,7 +10275,7 @@
           <t>SPKLU CIARO NAGREG</t>
         </is>
       </c>
-      <c r="D206" s="8" t="inlineStr">
+      <c r="D206" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9073,12 +10296,18 @@
         </is>
       </c>
       <c r="H206" s="6" t="n">
+        <v>-7.035922</v>
+      </c>
+      <c r="I206" s="6" t="n">
+        <v>107.92704</v>
+      </c>
+      <c r="J206" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="I206" s="7" t="n">
+      <c r="K206" s="8" t="n">
         <v>604.63</v>
       </c>
-      <c r="J206" s="6" t="n">
+      <c r="L206" s="7" t="n">
         <v>1580940</v>
       </c>
     </row>
@@ -9094,7 +10323,7 @@
           <t>SPKLU PLN ULP CIMAHI SELATAN</t>
         </is>
       </c>
-      <c r="D207" s="8" t="inlineStr">
+      <c r="D207" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9115,12 +10344,18 @@
         </is>
       </c>
       <c r="H207" s="6" t="n">
+        <v>-6.89858</v>
+      </c>
+      <c r="I207" s="6" t="n">
+        <v>107.554142</v>
+      </c>
+      <c r="J207" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="I207" s="7" t="n">
+      <c r="K207" s="8" t="n">
         <v>585.64</v>
       </c>
-      <c r="J207" s="6" t="n">
+      <c r="L207" s="7" t="n">
         <v>1444583</v>
       </c>
     </row>
@@ -9157,12 +10392,18 @@
         </is>
       </c>
       <c r="H208" s="6" t="n">
+        <v>-6.500639</v>
+      </c>
+      <c r="I208" s="6" t="n">
+        <v>106.757442</v>
+      </c>
+      <c r="J208" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="I208" s="7" t="n">
+      <c r="K208" s="8" t="n">
         <v>584.64</v>
       </c>
-      <c r="J208" s="6" t="n">
+      <c r="L208" s="7" t="n">
         <v>1514314</v>
       </c>
     </row>
@@ -9178,7 +10419,7 @@
           <t>SPKLU PLN SENTRA KIIC</t>
         </is>
       </c>
-      <c r="D209" s="8" t="inlineStr">
+      <c r="D209" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9199,12 +10440,18 @@
         </is>
       </c>
       <c r="H209" s="6" t="n">
+        <v>-6.357892</v>
+      </c>
+      <c r="I209" s="6" t="n">
+        <v>107.282226</v>
+      </c>
+      <c r="J209" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="I209" s="7" t="n">
+      <c r="K209" s="8" t="n">
         <v>582.14</v>
       </c>
-      <c r="J209" s="6" t="n">
+      <c r="L209" s="7" t="n">
         <v>1493456</v>
       </c>
     </row>
@@ -9241,12 +10488,18 @@
         </is>
       </c>
       <c r="H210" s="6" t="n">
+        <v>-6.650524</v>
+      </c>
+      <c r="I210" s="6" t="n">
+        <v>106.89581</v>
+      </c>
+      <c r="J210" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="I210" s="7" t="n">
+      <c r="K210" s="8" t="n">
         <v>575.5599999999999</v>
       </c>
-      <c r="J210" s="6" t="n">
+      <c r="L210" s="7" t="n">
         <v>1490604</v>
       </c>
     </row>
@@ -9262,7 +10515,7 @@
           <t>SPKLU GOLF JATINANGOR</t>
         </is>
       </c>
-      <c r="D211" s="8" t="inlineStr">
+      <c r="D211" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9283,12 +10536,18 @@
         </is>
       </c>
       <c r="H211" s="6" t="n">
+        <v>-6.91148</v>
+      </c>
+      <c r="I211" s="6" t="n">
+        <v>107.76274</v>
+      </c>
+      <c r="J211" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="I211" s="7" t="n">
+      <c r="K211" s="8" t="n">
         <v>575.01</v>
       </c>
-      <c r="J211" s="6" t="n">
+      <c r="L211" s="7" t="n">
         <v>1503545</v>
       </c>
     </row>
@@ -9304,7 +10563,7 @@
           <t>SPKLU PLN ULP KUNINGAN</t>
         </is>
       </c>
-      <c r="D212" s="8" t="inlineStr">
+      <c r="D212" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9325,12 +10584,18 @@
         </is>
       </c>
       <c r="H212" s="6" t="n">
+        <v>-6.97758</v>
+      </c>
+      <c r="I212" s="6" t="n">
+        <v>108.484629</v>
+      </c>
+      <c r="J212" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="I212" s="7" t="n">
+      <c r="K212" s="8" t="n">
         <v>572.03</v>
       </c>
-      <c r="J212" s="6" t="n">
+      <c r="L212" s="7" t="n">
         <v>1509835</v>
       </c>
     </row>
@@ -9346,7 +10611,7 @@
           <t>SPKLU PLN PATRA HOTEL AND CONVENTION</t>
         </is>
       </c>
-      <c r="D213" s="8" t="inlineStr">
+      <c r="D213" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9367,12 +10632,18 @@
         </is>
       </c>
       <c r="H213" s="6" t="n">
+        <v>-6.710243</v>
+      </c>
+      <c r="I213" s="6" t="n">
+        <v>108.533955</v>
+      </c>
+      <c r="J213" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="I213" s="7" t="n">
+      <c r="K213" s="8" t="n">
         <v>560.9</v>
       </c>
-      <c r="J213" s="6" t="n">
+      <c r="L213" s="7" t="n">
         <v>1494253</v>
       </c>
     </row>
@@ -9388,7 +10659,7 @@
           <t>SPKLU PLN ASTAKAIA</t>
         </is>
       </c>
-      <c r="D214" s="8" t="inlineStr">
+      <c r="D214" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9409,12 +10680,18 @@
         </is>
       </c>
       <c r="H214" s="6" t="n">
+        <v>-7.104176</v>
+      </c>
+      <c r="I214" s="6" t="n">
+        <v>107.453892</v>
+      </c>
+      <c r="J214" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="I214" s="7" t="n">
+      <c r="K214" s="8" t="n">
         <v>552.02</v>
       </c>
-      <c r="J214" s="6" t="n">
+      <c r="L214" s="7" t="n">
         <v>1443341</v>
       </c>
     </row>
@@ -9430,7 +10707,7 @@
           <t>SPKLU PLN Grand Inna Samudra Beach Hotel</t>
         </is>
       </c>
-      <c r="D215" s="8" t="inlineStr">
+      <c r="D215" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9451,12 +10728,18 @@
         </is>
       </c>
       <c r="H215" s="6" t="n">
+        <v>-6.962856</v>
+      </c>
+      <c r="I215" s="6" t="n">
+        <v>106.506872</v>
+      </c>
+      <c r="J215" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="I215" s="7" t="n">
+      <c r="K215" s="8" t="n">
         <v>547.61</v>
       </c>
-      <c r="J215" s="6" t="n">
+      <c r="L215" s="7" t="n">
         <v>1431831</v>
       </c>
     </row>
@@ -9472,7 +10755,7 @@
           <t>SPKLU PLN ULP JATIWANGI</t>
         </is>
       </c>
-      <c r="D216" s="8" t="inlineStr">
+      <c r="D216" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9493,12 +10776,18 @@
         </is>
       </c>
       <c r="H216" s="6" t="n">
+        <v>-6.726921</v>
+      </c>
+      <c r="I216" s="6" t="n">
+        <v>108.271809</v>
+      </c>
+      <c r="J216" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="I216" s="7" t="n">
+      <c r="K216" s="8" t="n">
         <v>541.54</v>
       </c>
-      <c r="J216" s="6" t="n">
+      <c r="L216" s="7" t="n">
         <v>1335878</v>
       </c>
     </row>
@@ -9514,7 +10803,7 @@
           <t>SPKLU PLN Pengadilan Negeri Subang</t>
         </is>
       </c>
-      <c r="D217" s="8" t="inlineStr">
+      <c r="D217" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9535,12 +10824,18 @@
         </is>
       </c>
       <c r="H217" s="6" t="n">
+        <v>-6.559086</v>
+      </c>
+      <c r="I217" s="6" t="n">
+        <v>107.770159</v>
+      </c>
+      <c r="J217" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="I217" s="7" t="n">
+      <c r="K217" s="8" t="n">
         <v>524.3099999999999</v>
       </c>
-      <c r="J217" s="6" t="n">
+      <c r="L217" s="7" t="n">
         <v>1422706</v>
       </c>
     </row>
@@ -9577,12 +10872,18 @@
         </is>
       </c>
       <c r="H218" s="6" t="n">
+        <v>-6.4761548</v>
+      </c>
+      <c r="I218" s="6" t="n">
+        <v>106.8637273</v>
+      </c>
+      <c r="J218" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="I218" s="7" t="n">
+      <c r="K218" s="8" t="n">
         <v>522.65</v>
       </c>
-      <c r="J218" s="6" t="n">
+      <c r="L218" s="7" t="n">
         <v>1353728</v>
       </c>
     </row>
@@ -9619,12 +10920,18 @@
         </is>
       </c>
       <c r="H219" s="6" t="n">
+        <v>-6.305559</v>
+      </c>
+      <c r="I219" s="6" t="n">
+        <v>107.292548</v>
+      </c>
+      <c r="J219" s="7" t="n">
         <v>105</v>
       </c>
-      <c r="I219" s="7" t="n">
+      <c r="K219" s="8" t="n">
         <v>502.97</v>
       </c>
-      <c r="J219" s="6" t="n">
+      <c r="L219" s="7" t="n">
         <v>1290302</v>
       </c>
     </row>
@@ -9640,7 +10947,7 @@
           <t>SPKLU PLN ULP UJUNGBERUNG</t>
         </is>
       </c>
-      <c r="D220" s="8" t="inlineStr">
+      <c r="D220" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9661,12 +10968,18 @@
         </is>
       </c>
       <c r="H220" s="6" t="n">
+        <v>-6.913408</v>
+      </c>
+      <c r="I220" s="6" t="n">
+        <v>107.694866</v>
+      </c>
+      <c r="J220" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="I220" s="7" t="n">
+      <c r="K220" s="8" t="n">
         <v>497.83</v>
       </c>
-      <c r="J220" s="6" t="n">
+      <c r="L220" s="7" t="n">
         <v>1326212</v>
       </c>
     </row>
@@ -9682,7 +10995,7 @@
           <t>SPKLU Hotel Fitra Majalengka</t>
         </is>
       </c>
-      <c r="D221" s="8" t="inlineStr">
+      <c r="D221" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9703,12 +11016,18 @@
         </is>
       </c>
       <c r="H221" s="6" t="n">
+        <v>-6.832486</v>
+      </c>
+      <c r="I221" s="6" t="n">
+        <v>108.209385</v>
+      </c>
+      <c r="J221" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="I221" s="7" t="n">
+      <c r="K221" s="8" t="n">
         <v>493.14</v>
       </c>
-      <c r="J221" s="6" t="n">
+      <c r="L221" s="7" t="n">
         <v>1216433</v>
       </c>
     </row>
@@ -9724,7 +11043,7 @@
           <t>SPKLU PLN ULP CIKEDUNG</t>
         </is>
       </c>
-      <c r="D222" s="8" t="inlineStr">
+      <c r="D222" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9745,12 +11064,18 @@
         </is>
       </c>
       <c r="H222" s="6" t="n">
+        <v>-6.406077</v>
+      </c>
+      <c r="I222" s="6" t="n">
+        <v>108.169036</v>
+      </c>
+      <c r="J222" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="I222" s="7" t="n">
+      <c r="K222" s="8" t="n">
         <v>492.74</v>
       </c>
-      <c r="J222" s="6" t="n">
+      <c r="L222" s="7" t="n">
         <v>1288335</v>
       </c>
     </row>
@@ -9766,7 +11091,7 @@
           <t>SPKLU PLN RS AU dr M Hassan Toto</t>
         </is>
       </c>
-      <c r="D223" s="8" t="inlineStr">
+      <c r="D223" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9787,12 +11112,18 @@
         </is>
       </c>
       <c r="H223" s="6" t="n">
+        <v>-6.544656</v>
+      </c>
+      <c r="I223" s="6" t="n">
+        <v>106.762061</v>
+      </c>
+      <c r="J223" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="I223" s="7" t="n">
+      <c r="K223" s="8" t="n">
         <v>490.04</v>
       </c>
-      <c r="J223" s="6" t="n">
+      <c r="L223" s="7" t="n">
         <v>1269285</v>
       </c>
     </row>
@@ -9808,7 +11139,7 @@
           <t>SPKLU The Allure Villas Pangandaran</t>
         </is>
       </c>
-      <c r="D224" s="8" t="inlineStr">
+      <c r="D224" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9829,12 +11160,18 @@
         </is>
       </c>
       <c r="H224" s="6" t="n">
+        <v>-7.6845285</v>
+      </c>
+      <c r="I224" s="6" t="n">
+        <v>108.6383622</v>
+      </c>
+      <c r="J224" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="I224" s="7" t="n">
+      <c r="K224" s="8" t="n">
         <v>485.52</v>
       </c>
-      <c r="J224" s="6" t="n">
+      <c r="L224" s="7" t="n">
         <v>1317316</v>
       </c>
     </row>
@@ -9850,7 +11187,7 @@
           <t>SPKLU PLN KAJENE FOREST KUNINGAN</t>
         </is>
       </c>
-      <c r="D225" s="8" t="inlineStr">
+      <c r="D225" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9871,12 +11208,18 @@
         </is>
       </c>
       <c r="H225" s="6" t="n">
+        <v>-6.972639</v>
+      </c>
+      <c r="I225" s="6" t="n">
+        <v>108.485448</v>
+      </c>
+      <c r="J225" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="I225" s="7" t="n">
+      <c r="K225" s="8" t="n">
         <v>475.71</v>
       </c>
-      <c r="J225" s="6" t="n">
+      <c r="L225" s="7" t="n">
         <v>1255634</v>
       </c>
     </row>
@@ -9892,7 +11235,7 @@
           <t>SPKLU PLN ULP LELES</t>
         </is>
       </c>
-      <c r="D226" s="8" t="inlineStr">
+      <c r="D226" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9913,12 +11256,18 @@
         </is>
       </c>
       <c r="H226" s="6" t="n">
+        <v>-7.10007</v>
+      </c>
+      <c r="I226" s="6" t="n">
+        <v>107.8984</v>
+      </c>
+      <c r="J226" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="I226" s="7" t="n">
+      <c r="K226" s="8" t="n">
         <v>467.26</v>
       </c>
-      <c r="J226" s="6" t="n">
+      <c r="L226" s="7" t="n">
         <v>1210267</v>
       </c>
     </row>
@@ -9934,7 +11283,7 @@
           <t>SPKLU PLN HOTEL LASKA CILETUH PELABUHAN RATU</t>
         </is>
       </c>
-      <c r="D227" s="8" t="inlineStr">
+      <c r="D227" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -9955,12 +11304,18 @@
         </is>
       </c>
       <c r="H227" s="6" t="n">
+        <v>-7.1207447</v>
+      </c>
+      <c r="I227" s="6" t="n">
+        <v>106.4781087</v>
+      </c>
+      <c r="J227" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="I227" s="7" t="n">
+      <c r="K227" s="8" t="n">
         <v>451.2</v>
       </c>
-      <c r="J227" s="6" t="n">
+      <c r="L227" s="7" t="n">
         <v>1168665</v>
       </c>
     </row>
@@ -9997,12 +11352,18 @@
         </is>
       </c>
       <c r="H228" s="6" t="n">
+        <v>-6.690258</v>
+      </c>
+      <c r="I228" s="6" t="n">
+        <v>106.942722</v>
+      </c>
+      <c r="J228" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="I228" s="7" t="n">
+      <c r="K228" s="8" t="n">
         <v>447.91</v>
       </c>
-      <c r="J228" s="6" t="n">
+      <c r="L228" s="7" t="n">
         <v>1160166</v>
       </c>
     </row>
@@ -10018,7 +11379,7 @@
           <t>SPKLU PLN ULP JATIBARANG</t>
         </is>
       </c>
-      <c r="D229" s="8" t="inlineStr">
+      <c r="D229" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10039,12 +11400,18 @@
         </is>
       </c>
       <c r="H229" s="6" t="n">
+        <v>-6.4759881</v>
+      </c>
+      <c r="I229" s="6" t="n">
+        <v>108.303677</v>
+      </c>
+      <c r="J229" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="I229" s="7" t="n">
+      <c r="K229" s="8" t="n">
         <v>443.64</v>
       </c>
-      <c r="J229" s="6" t="n">
+      <c r="L229" s="7" t="n">
         <v>1159984</v>
       </c>
     </row>
@@ -10060,7 +11427,7 @@
           <t>SPKLU PLN ULP CILIMUS</t>
         </is>
       </c>
-      <c r="D230" s="8" t="inlineStr">
+      <c r="D230" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10081,12 +11448,18 @@
         </is>
       </c>
       <c r="H230" s="6" t="n">
+        <v>-6.877373</v>
+      </c>
+      <c r="I230" s="6" t="n">
+        <v>108.496024</v>
+      </c>
+      <c r="J230" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="I230" s="7" t="n">
+      <c r="K230" s="8" t="n">
         <v>438.61</v>
       </c>
-      <c r="J230" s="6" t="n">
+      <c r="L230" s="7" t="n">
         <v>1157659</v>
       </c>
     </row>
@@ -10102,7 +11475,7 @@
           <t>SPKLU PLN ULP KOPO</t>
         </is>
       </c>
-      <c r="D231" s="8" t="inlineStr">
+      <c r="D231" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10123,12 +11496,18 @@
         </is>
       </c>
       <c r="H231" s="6" t="n">
+        <v>-6.933984</v>
+      </c>
+      <c r="I231" s="6" t="n">
+        <v>107.57149</v>
+      </c>
+      <c r="J231" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="I231" s="7" t="n">
+      <c r="K231" s="8" t="n">
         <v>428.29</v>
       </c>
-      <c r="J231" s="6" t="n">
+      <c r="L231" s="7" t="n">
         <v>1141025</v>
       </c>
     </row>
@@ -10144,7 +11523,7 @@
           <t>SPKLU PLN FAVE HOTEL GARUT</t>
         </is>
       </c>
-      <c r="D232" s="8" t="inlineStr">
+      <c r="D232" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10165,12 +11544,18 @@
         </is>
       </c>
       <c r="H232" s="6" t="n">
+        <v>-7.20409</v>
+      </c>
+      <c r="I232" s="6" t="n">
+        <v>107.8893</v>
+      </c>
+      <c r="J232" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="I232" s="7" t="n">
+      <c r="K232" s="8" t="n">
         <v>427.3</v>
       </c>
-      <c r="J232" s="6" t="n">
+      <c r="L232" s="7" t="n">
         <v>1106788</v>
       </c>
     </row>
@@ -10186,7 +11571,7 @@
           <t>SPKLU PLN TRANSMART CIPADUNG</t>
         </is>
       </c>
-      <c r="D233" s="8" t="inlineStr">
+      <c r="D233" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10207,12 +11592,18 @@
         </is>
       </c>
       <c r="H233" s="6" t="n">
+        <v>-6.925675</v>
+      </c>
+      <c r="I233" s="6" t="n">
+        <v>107.710927</v>
+      </c>
+      <c r="J233" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="I233" s="7" t="n">
+      <c r="K233" s="8" t="n">
         <v>427.12</v>
       </c>
-      <c r="J233" s="6" t="n">
+      <c r="L233" s="7" t="n">
         <v>1137803</v>
       </c>
     </row>
@@ -10228,7 +11619,7 @@
           <t>SPKLU PLN HOTEL GREENPEAK CISARUA</t>
         </is>
       </c>
-      <c r="D234" s="8" t="inlineStr">
+      <c r="D234" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10249,12 +11640,18 @@
         </is>
       </c>
       <c r="H234" s="6" t="n">
+        <v>-6.657776</v>
+      </c>
+      <c r="I234" s="6" t="n">
+        <v>106.909107</v>
+      </c>
+      <c r="J234" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="I234" s="7" t="n">
+      <c r="K234" s="8" t="n">
         <v>423.34</v>
       </c>
-      <c r="J234" s="6" t="n">
+      <c r="L234" s="7" t="n">
         <v>1096475</v>
       </c>
     </row>
@@ -10270,7 +11667,7 @@
           <t>SPKLU PLN ULP CIKEMBAR</t>
         </is>
       </c>
-      <c r="D235" s="8" t="inlineStr">
+      <c r="D235" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10291,12 +11688,18 @@
         </is>
       </c>
       <c r="H235" s="6" t="n">
+        <v>-6.9512542</v>
+      </c>
+      <c r="I235" s="6" t="n">
+        <v>106.7694679</v>
+      </c>
+      <c r="J235" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="I235" s="7" t="n">
+      <c r="K235" s="8" t="n">
         <v>420.2</v>
       </c>
-      <c r="J235" s="6" t="n">
+      <c r="L235" s="7" t="n">
         <v>1098648</v>
       </c>
     </row>
@@ -10312,7 +11715,7 @@
           <t>SPKLU PLN Forest Hills Hotel Ciwidey</t>
         </is>
       </c>
-      <c r="D236" s="8" t="inlineStr">
+      <c r="D236" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10333,12 +11736,18 @@
         </is>
       </c>
       <c r="H236" s="6" t="n">
+        <v>-7.054734</v>
+      </c>
+      <c r="I236" s="6" t="n">
+        <v>107.499595</v>
+      </c>
+      <c r="J236" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="I236" s="7" t="n">
+      <c r="K236" s="8" t="n">
         <v>413.21</v>
       </c>
-      <c r="J236" s="6" t="n">
+      <c r="L236" s="7" t="n">
         <v>1080464</v>
       </c>
     </row>
@@ -10354,7 +11763,7 @@
           <t>SPKLU PLN ULP MAJALAYA KOTA</t>
         </is>
       </c>
-      <c r="D237" s="8" t="inlineStr">
+      <c r="D237" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10375,12 +11784,18 @@
         </is>
       </c>
       <c r="H237" s="6" t="n">
+        <v>-7.051372</v>
+      </c>
+      <c r="I237" s="6" t="n">
+        <v>107.761095</v>
+      </c>
+      <c r="J237" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="I237" s="7" t="n">
+      <c r="K237" s="8" t="n">
         <v>408.1</v>
       </c>
-      <c r="J237" s="6" t="n">
+      <c r="L237" s="7" t="n">
         <v>1067070</v>
       </c>
     </row>
@@ -10396,7 +11811,7 @@
           <t>SPKLU PLN UP3 CIKARANG</t>
         </is>
       </c>
-      <c r="D238" s="8" t="inlineStr">
+      <c r="D238" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10417,12 +11832,18 @@
         </is>
       </c>
       <c r="H238" s="6" t="n">
+        <v>-6.365536</v>
+      </c>
+      <c r="I238" s="6" t="n">
+        <v>107.179561</v>
+      </c>
+      <c r="J238" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="I238" s="7" t="n">
+      <c r="K238" s="8" t="n">
         <v>406.94</v>
       </c>
-      <c r="J238" s="6" t="n">
+      <c r="L238" s="7" t="n">
         <v>1054017</v>
       </c>
     </row>
@@ -10438,7 +11859,7 @@
           <t>SPKLU PLN PR Bali Resort Bogor</t>
         </is>
       </c>
-      <c r="D239" s="8" t="inlineStr">
+      <c r="D239" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10459,12 +11880,18 @@
         </is>
       </c>
       <c r="H239" s="6" t="n">
+        <v>-6.537597</v>
+      </c>
+      <c r="I239" s="6" t="n">
+        <v>106.740143</v>
+      </c>
+      <c r="J239" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="I239" s="7" t="n">
+      <c r="K239" s="8" t="n">
         <v>402.8</v>
       </c>
-      <c r="J239" s="6" t="n">
+      <c r="L239" s="7" t="n">
         <v>1043319</v>
       </c>
     </row>
@@ -10480,7 +11907,7 @@
           <t>SPKLU PLN ULP MAJALAYA KOTA</t>
         </is>
       </c>
-      <c r="D240" s="8" t="inlineStr">
+      <c r="D240" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10501,12 +11928,18 @@
         </is>
       </c>
       <c r="H240" s="6" t="n">
+        <v>-7.051372</v>
+      </c>
+      <c r="I240" s="6" t="n">
+        <v>107.761095</v>
+      </c>
+      <c r="J240" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="I240" s="7" t="n">
+      <c r="K240" s="8" t="n">
         <v>387.82</v>
       </c>
-      <c r="J240" s="6" t="n">
+      <c r="L240" s="7" t="n">
         <v>1014049</v>
       </c>
     </row>
@@ -10522,7 +11955,7 @@
           <t>SPKLU PLN ULP BANJARAN</t>
         </is>
       </c>
-      <c r="D241" s="8" t="inlineStr">
+      <c r="D241" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10543,12 +11976,18 @@
         </is>
       </c>
       <c r="H241" s="6" t="n">
+        <v>-7.035417</v>
+      </c>
+      <c r="I241" s="6" t="n">
+        <v>107.593316</v>
+      </c>
+      <c r="J241" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="I241" s="7" t="n">
+      <c r="K241" s="8" t="n">
         <v>384.77</v>
       </c>
-      <c r="J241" s="6" t="n">
+      <c r="L241" s="7" t="n">
         <v>1006116</v>
       </c>
     </row>
@@ -10564,7 +12003,7 @@
           <t>SPKLU PLN TRANSMART CIMAHI</t>
         </is>
       </c>
-      <c r="D242" s="8" t="inlineStr">
+      <c r="D242" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10585,12 +12024,18 @@
         </is>
       </c>
       <c r="H242" s="6" t="n">
+        <v>-6.869391</v>
+      </c>
+      <c r="I242" s="6" t="n">
+        <v>107.53321</v>
+      </c>
+      <c r="J242" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="I242" s="7" t="n">
+      <c r="K242" s="8" t="n">
         <v>377.15</v>
       </c>
-      <c r="J242" s="6" t="n">
+      <c r="L242" s="7" t="n">
         <v>930323</v>
       </c>
     </row>
@@ -10606,7 +12051,7 @@
           <t>SPKLU EV LOKA WAROENG KEBOENKOE</t>
         </is>
       </c>
-      <c r="D243" s="8" t="inlineStr">
+      <c r="D243" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10627,12 +12072,18 @@
         </is>
       </c>
       <c r="H243" s="6" t="n">
+        <v>-6.414687</v>
+      </c>
+      <c r="I243" s="6" t="n">
+        <v>106.899063</v>
+      </c>
+      <c r="J243" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="I243" s="7" t="n">
+      <c r="K243" s="8" t="n">
         <v>376.15</v>
       </c>
-      <c r="J243" s="6" t="n">
+      <c r="L243" s="7" t="n">
         <v>965005</v>
       </c>
     </row>
@@ -10648,7 +12099,7 @@
           <t>SPKLU PLN POSKO PANGALENGAN</t>
         </is>
       </c>
-      <c r="D244" s="8" t="inlineStr">
+      <c r="D244" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10669,12 +12120,18 @@
         </is>
       </c>
       <c r="H244" s="6" t="n">
+        <v>-7.17627</v>
+      </c>
+      <c r="I244" s="6" t="n">
+        <v>107.572329</v>
+      </c>
+      <c r="J244" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="I244" s="7" t="n">
+      <c r="K244" s="8" t="n">
         <v>375.41</v>
       </c>
-      <c r="J244" s="6" t="n">
+      <c r="L244" s="7" t="n">
         <v>981640</v>
       </c>
     </row>
@@ -10690,7 +12147,7 @@
           <t>SPKLU PLN ULP PELABUHAN RATU</t>
         </is>
       </c>
-      <c r="D245" s="8" t="inlineStr">
+      <c r="D245" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10711,12 +12168,18 @@
         </is>
       </c>
       <c r="H245" s="6" t="n">
+        <v>-6.9869478</v>
+      </c>
+      <c r="I245" s="6" t="n">
+        <v>106.5556702</v>
+      </c>
+      <c r="J245" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="I245" s="7" t="n">
+      <c r="K245" s="8" t="n">
         <v>365.2</v>
       </c>
-      <c r="J245" s="6" t="n">
+      <c r="L245" s="7" t="n">
         <v>954921</v>
       </c>
     </row>
@@ -10732,7 +12195,7 @@
           <t>SPKLU PLN ULP KARANGNUNGGAL</t>
         </is>
       </c>
-      <c r="D246" s="8" t="inlineStr">
+      <c r="D246" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10753,12 +12216,18 @@
         </is>
       </c>
       <c r="H246" s="6" t="n">
+        <v>-7.6318453</v>
+      </c>
+      <c r="I246" s="6" t="n">
+        <v>108.1329428</v>
+      </c>
+      <c r="J246" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="I246" s="7" t="n">
+      <c r="K246" s="8" t="n">
         <v>362.62</v>
       </c>
-      <c r="J246" s="6" t="n">
+      <c r="L246" s="7" t="n">
         <v>983915</v>
       </c>
     </row>
@@ -10795,12 +12264,18 @@
         </is>
       </c>
       <c r="H247" s="6" t="n">
+        <v>-6.515805</v>
+      </c>
+      <c r="I247" s="6" t="n">
+        <v>106.756985</v>
+      </c>
+      <c r="J247" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="I247" s="7" t="n">
+      <c r="K247" s="8" t="n">
         <v>358.77</v>
       </c>
-      <c r="J247" s="6" t="n">
+      <c r="L247" s="7" t="n">
         <v>929156</v>
       </c>
     </row>
@@ -10816,7 +12291,7 @@
           <t>SPKLU PLN KANTOR IMIGRASI BEKASI</t>
         </is>
       </c>
-      <c r="D248" s="8" t="inlineStr">
+      <c r="D248" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10837,12 +12312,18 @@
         </is>
       </c>
       <c r="H248" s="6" t="n">
+        <v>-6.21952</v>
+      </c>
+      <c r="I248" s="6" t="n">
+        <v>107.0302</v>
+      </c>
+      <c r="J248" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="I248" s="7" t="n">
+      <c r="K248" s="8" t="n">
         <v>358.16</v>
       </c>
-      <c r="J248" s="6" t="n">
+      <c r="L248" s="7" t="n">
         <v>954178</v>
       </c>
     </row>
@@ -10858,7 +12339,7 @@
           <t>SPKLU PLN ULP CIREBON KOTA</t>
         </is>
       </c>
-      <c r="D249" s="8" t="inlineStr">
+      <c r="D249" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10879,12 +12360,18 @@
         </is>
       </c>
       <c r="H249" s="6" t="n">
+        <v>-6.7212184</v>
+      </c>
+      <c r="I249" s="6" t="n">
+        <v>108.5721242</v>
+      </c>
+      <c r="J249" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="I249" s="7" t="n">
+      <c r="K249" s="8" t="n">
         <v>355.58</v>
       </c>
-      <c r="J249" s="6" t="n">
+      <c r="L249" s="7" t="n">
         <v>920954</v>
       </c>
     </row>
@@ -10900,7 +12387,7 @@
           <t>SPKLU PLN ULP CIPANAS</t>
         </is>
       </c>
-      <c r="D250" s="8" t="inlineStr">
+      <c r="D250" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10921,12 +12408,18 @@
         </is>
       </c>
       <c r="H250" s="6" t="n">
+        <v>-6.734727</v>
+      </c>
+      <c r="I250" s="6" t="n">
+        <v>107.041681</v>
+      </c>
+      <c r="J250" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="I250" s="7" t="n">
+      <c r="K250" s="8" t="n">
         <v>351.89</v>
       </c>
-      <c r="J250" s="6" t="n">
+      <c r="L250" s="7" t="n">
         <v>920081</v>
       </c>
     </row>
@@ -10942,7 +12435,7 @@
           <t>SPKLU PLN ULP JASINGA</t>
         </is>
       </c>
-      <c r="D251" s="8" t="inlineStr">
+      <c r="D251" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -10963,12 +12456,18 @@
         </is>
       </c>
       <c r="H251" s="6" t="n">
+        <v>-6.520282</v>
+      </c>
+      <c r="I251" s="6" t="n">
+        <v>106.498591</v>
+      </c>
+      <c r="J251" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="I251" s="7" t="n">
+      <c r="K251" s="8" t="n">
         <v>348.57</v>
       </c>
-      <c r="J251" s="6" t="n">
+      <c r="L251" s="7" t="n">
         <v>902850</v>
       </c>
     </row>
@@ -10984,7 +12483,7 @@
           <t>SPKLU PLN POLRES CIANJUR</t>
         </is>
       </c>
-      <c r="D252" s="8" t="inlineStr">
+      <c r="D252" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11005,12 +12504,18 @@
         </is>
       </c>
       <c r="H252" s="6" t="n">
+        <v>-6.836306</v>
+      </c>
+      <c r="I252" s="6" t="n">
+        <v>107.122259</v>
+      </c>
+      <c r="J252" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="I252" s="7" t="n">
+      <c r="K252" s="8" t="n">
         <v>348.05</v>
       </c>
-      <c r="J252" s="6" t="n">
+      <c r="L252" s="7" t="n">
         <v>910087</v>
       </c>
     </row>
@@ -11026,7 +12531,7 @@
           <t>SPKLU REST AREA KM 101 B RUAS CIPALI (SC)</t>
         </is>
       </c>
-      <c r="D253" s="8" t="inlineStr">
+      <c r="D253" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11047,12 +12552,18 @@
         </is>
       </c>
       <c r="H253" s="6" t="n">
+        <v>-6.5091024</v>
+      </c>
+      <c r="I253" s="6" t="n">
+        <v>107.7186932</v>
+      </c>
+      <c r="J253" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="I253" s="7" t="n">
+      <c r="K253" s="8" t="n">
         <v>345.32</v>
       </c>
-      <c r="J253" s="6" t="n">
+      <c r="L253" s="7" t="n">
         <v>936922</v>
       </c>
     </row>
@@ -11068,7 +12579,7 @@
           <t>SPKLU PLN HOTEL NOVENA</t>
         </is>
       </c>
-      <c r="D254" s="8" t="inlineStr">
+      <c r="D254" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11089,12 +12600,18 @@
         </is>
       </c>
       <c r="H254" s="6" t="n">
+        <v>-6.840745</v>
+      </c>
+      <c r="I254" s="6" t="n">
+        <v>107.597386</v>
+      </c>
+      <c r="J254" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="I254" s="7" t="n">
+      <c r="K254" s="8" t="n">
         <v>332.08</v>
       </c>
-      <c r="J254" s="6" t="n">
+      <c r="L254" s="7" t="n">
         <v>843727</v>
       </c>
     </row>
@@ -11110,7 +12627,7 @@
           <t>SPKLU PLN ULP RAJAPOLAH</t>
         </is>
       </c>
-      <c r="D255" s="8" t="inlineStr">
+      <c r="D255" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11131,12 +12648,18 @@
         </is>
       </c>
       <c r="H255" s="6" t="n">
+        <v>-7.2271177</v>
+      </c>
+      <c r="I255" s="6" t="n">
+        <v>108.1899931</v>
+      </c>
+      <c r="J255" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="I255" s="7" t="n">
+      <c r="K255" s="8" t="n">
         <v>331.64</v>
       </c>
-      <c r="J255" s="6" t="n">
+      <c r="L255" s="7" t="n">
         <v>899864</v>
       </c>
     </row>
@@ -11152,7 +12675,7 @@
           <t>SPKLU PLN ULP RANCAEKEK</t>
         </is>
       </c>
-      <c r="D256" s="8" t="inlineStr">
+      <c r="D256" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11173,12 +12696,18 @@
         </is>
       </c>
       <c r="H256" s="6" t="n">
+        <v>-6.95895</v>
+      </c>
+      <c r="I256" s="6" t="n">
+        <v>107.76474</v>
+      </c>
+      <c r="J256" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="I256" s="7" t="n">
+      <c r="K256" s="8" t="n">
         <v>324.47</v>
       </c>
-      <c r="J256" s="6" t="n">
+      <c r="L256" s="7" t="n">
         <v>848371</v>
       </c>
     </row>
@@ -11194,7 +12723,7 @@
           <t>SPKLU PLN ULP PAMEUNGPEUK</t>
         </is>
       </c>
-      <c r="D257" s="8" t="inlineStr">
+      <c r="D257" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11215,12 +12744,18 @@
         </is>
       </c>
       <c r="H257" s="6" t="n">
+        <v>-7.6465524</v>
+      </c>
+      <c r="I257" s="6" t="n">
+        <v>107.7085562</v>
+      </c>
+      <c r="J257" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="I257" s="7" t="n">
+      <c r="K257" s="8" t="n">
         <v>318.73</v>
       </c>
-      <c r="J257" s="6" t="n">
+      <c r="L257" s="7" t="n">
         <v>825559</v>
       </c>
     </row>
@@ -11236,7 +12771,7 @@
           <t>SPKLU PLN TERAS TEH POPI</t>
         </is>
       </c>
-      <c r="D258" s="8" t="inlineStr">
+      <c r="D258" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11257,12 +12792,18 @@
         </is>
       </c>
       <c r="H258" s="6" t="n">
+        <v>-6.542711</v>
+      </c>
+      <c r="I258" s="6" t="n">
+        <v>106.812466</v>
+      </c>
+      <c r="J258" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="I258" s="7" t="n">
+      <c r="K258" s="8" t="n">
         <v>309.88</v>
       </c>
-      <c r="J258" s="6" t="n">
+      <c r="L258" s="7" t="n">
         <v>802603</v>
       </c>
     </row>
@@ -11299,12 +12840,18 @@
         </is>
       </c>
       <c r="H259" s="6" t="n">
+        <v>-7.0168617</v>
+      </c>
+      <c r="I259" s="6" t="n">
+        <v>107.8822559</v>
+      </c>
+      <c r="J259" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="I259" s="7" t="n">
+      <c r="K259" s="8" t="n">
         <v>307.71</v>
       </c>
-      <c r="J259" s="6" t="n">
+      <c r="L259" s="7" t="n">
         <v>804576</v>
       </c>
     </row>
@@ -11320,7 +12867,7 @@
           <t>SPKLU PLN Rengganis Campsite</t>
         </is>
       </c>
-      <c r="D260" s="8" t="inlineStr">
+      <c r="D260" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11341,12 +12888,18 @@
         </is>
       </c>
       <c r="H260" s="6" t="n">
+        <v>-7.161417</v>
+      </c>
+      <c r="I260" s="6" t="n">
+        <v>107.364287</v>
+      </c>
+      <c r="J260" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I260" s="7" t="n">
+      <c r="K260" s="8" t="n">
         <v>307.15</v>
       </c>
-      <c r="J260" s="6" t="n">
+      <c r="L260" s="7" t="n">
         <v>803114</v>
       </c>
     </row>
@@ -11362,7 +12915,7 @@
           <t>SPKLU PLN ULP TANJUNG SARI</t>
         </is>
       </c>
-      <c r="D261" s="8" t="inlineStr">
+      <c r="D261" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11383,12 +12936,18 @@
         </is>
       </c>
       <c r="H261" s="6" t="n">
+        <v>-6.896327</v>
+      </c>
+      <c r="I261" s="6" t="n">
+        <v>107.807858</v>
+      </c>
+      <c r="J261" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="I261" s="7" t="n">
+      <c r="K261" s="8" t="n">
         <v>293.73</v>
       </c>
-      <c r="J261" s="6" t="n">
+      <c r="L261" s="7" t="n">
         <v>768055</v>
       </c>
     </row>
@@ -11404,7 +12963,7 @@
           <t>SPKLU PABERIK BADJOE</t>
         </is>
       </c>
-      <c r="D262" s="8" t="inlineStr">
+      <c r="D262" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11425,12 +12984,18 @@
         </is>
       </c>
       <c r="H262" s="6" t="n">
+        <v>-6.945709</v>
+      </c>
+      <c r="I262" s="6" t="n">
+        <v>107.638621</v>
+      </c>
+      <c r="J262" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="I262" s="7" t="n">
+      <c r="K262" s="8" t="n">
         <v>293.16</v>
       </c>
-      <c r="J262" s="6" t="n">
+      <c r="L262" s="7" t="n">
         <v>780986</v>
       </c>
     </row>
@@ -11446,7 +13011,7 @@
           <t>SPKLU PLN HOTEL HARPER PURWAKARTA</t>
         </is>
       </c>
-      <c r="D263" s="8" t="inlineStr">
+      <c r="D263" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11467,12 +13032,18 @@
         </is>
       </c>
       <c r="H263" s="6" t="n">
+        <v>-6.478788</v>
+      </c>
+      <c r="I263" s="6" t="n">
+        <v>107.481142</v>
+      </c>
+      <c r="J263" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="I263" s="7" t="n">
+      <c r="K263" s="8" t="n">
         <v>291.23</v>
       </c>
-      <c r="J263" s="6" t="n">
+      <c r="L263" s="7" t="n">
         <v>739909</v>
       </c>
     </row>
@@ -11488,7 +13059,7 @@
           <t>SPKLU PLN RESORT PRIMA CISARUA</t>
         </is>
       </c>
-      <c r="D264" s="8" t="inlineStr">
+      <c r="D264" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11509,12 +13080,18 @@
         </is>
       </c>
       <c r="H264" s="6" t="n">
+        <v>-6.702217</v>
+      </c>
+      <c r="I264" s="6" t="n">
+        <v>106.945356</v>
+      </c>
+      <c r="J264" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="I264" s="7" t="n">
+      <c r="K264" s="8" t="n">
         <v>289</v>
       </c>
-      <c r="J264" s="6" t="n">
+      <c r="L264" s="7" t="n">
         <v>748559</v>
       </c>
     </row>
@@ -11530,7 +13107,7 @@
           <t>SPKLU KOPI NAKO</t>
         </is>
       </c>
-      <c r="D265" s="8" t="inlineStr">
+      <c r="D265" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11551,12 +13128,18 @@
         </is>
       </c>
       <c r="H265" s="6" t="n">
+        <v>-6.81648</v>
+      </c>
+      <c r="I265" s="6" t="n">
+        <v>107.129972</v>
+      </c>
+      <c r="J265" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I265" s="7" t="n">
+      <c r="K265" s="8" t="n">
         <v>285</v>
       </c>
-      <c r="J265" s="6" t="n">
+      <c r="L265" s="7" t="n">
         <v>745328</v>
       </c>
     </row>
@@ -11572,7 +13155,7 @@
           <t>SPKLU PLN HOTEL NEWTON</t>
         </is>
       </c>
-      <c r="D266" s="8" t="inlineStr">
+      <c r="D266" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11593,12 +13176,18 @@
         </is>
       </c>
       <c r="H266" s="6" t="n">
+        <v>-6.914815</v>
+      </c>
+      <c r="I266" s="6" t="n">
+        <v>107.629944</v>
+      </c>
+      <c r="J266" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="I266" s="7" t="n">
+      <c r="K266" s="8" t="n">
         <v>280.55</v>
       </c>
-      <c r="J266" s="6" t="n">
+      <c r="L266" s="7" t="n">
         <v>747429</v>
       </c>
     </row>
@@ -11614,7 +13203,7 @@
           <t>SPKLU PLN Horison Tasikmalaya</t>
         </is>
       </c>
-      <c r="D267" s="8" t="inlineStr">
+      <c r="D267" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11635,12 +13224,18 @@
         </is>
       </c>
       <c r="H267" s="6" t="n">
+        <v>-7.3260345</v>
+      </c>
+      <c r="I267" s="6" t="n">
+        <v>108.2164</v>
+      </c>
+      <c r="J267" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="I267" s="7" t="n">
+      <c r="K267" s="8" t="n">
         <v>275.65</v>
       </c>
-      <c r="J267" s="6" t="n">
+      <c r="L267" s="7" t="n">
         <v>747926</v>
       </c>
     </row>
@@ -11656,7 +13251,7 @@
           <t>SPKLU PEMDA GARUT</t>
         </is>
       </c>
-      <c r="D268" s="8" t="inlineStr">
+      <c r="D268" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11677,12 +13272,18 @@
         </is>
       </c>
       <c r="H268" s="6" t="n">
+        <v>-7.21703</v>
+      </c>
+      <c r="I268" s="6" t="n">
+        <v>107.9016</v>
+      </c>
+      <c r="J268" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="I268" s="7" t="n">
+      <c r="K268" s="8" t="n">
         <v>271.48</v>
       </c>
-      <c r="J268" s="6" t="n">
+      <c r="L268" s="7" t="n">
         <v>703172</v>
       </c>
     </row>
@@ -11698,7 +13299,7 @@
           <t>SPKLU PLN Mall Pelayanan Publik Cimahi</t>
         </is>
       </c>
-      <c r="D269" s="8" t="inlineStr">
+      <c r="D269" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11719,12 +13320,18 @@
         </is>
       </c>
       <c r="H269" s="6" t="n">
+        <v>-6.882731</v>
+      </c>
+      <c r="I269" s="6" t="n">
+        <v>107.561482</v>
+      </c>
+      <c r="J269" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="I269" s="7" t="n">
+      <c r="K269" s="8" t="n">
         <v>269.37</v>
       </c>
-      <c r="J269" s="6" t="n">
+      <c r="L269" s="7" t="n">
         <v>664445</v>
       </c>
     </row>
@@ -11740,7 +13347,7 @@
           <t>SPKLU PLN ULP SINGAPARNA</t>
         </is>
       </c>
-      <c r="D270" s="8" t="inlineStr">
+      <c r="D270" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11761,12 +13368,18 @@
         </is>
       </c>
       <c r="H270" s="6" t="n">
+        <v>-7.3460317</v>
+      </c>
+      <c r="I270" s="6" t="n">
+        <v>108.1095447</v>
+      </c>
+      <c r="J270" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I270" s="7" t="n">
+      <c r="K270" s="8" t="n">
         <v>240.99</v>
       </c>
-      <c r="J270" s="6" t="n">
+      <c r="L270" s="7" t="n">
         <v>653809</v>
       </c>
     </row>
@@ -11782,7 +13395,7 @@
           <t>SPKLU Dinas Perhubungan Kabupaten Cianjur</t>
         </is>
       </c>
-      <c r="D271" s="8" t="inlineStr">
+      <c r="D271" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11803,12 +13416,18 @@
         </is>
       </c>
       <c r="H271" s="6" t="n">
+        <v>-6.809739</v>
+      </c>
+      <c r="I271" s="6" t="n">
+        <v>107.149535</v>
+      </c>
+      <c r="J271" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="I271" s="7" t="n">
+      <c r="K271" s="8" t="n">
         <v>240.7</v>
       </c>
-      <c r="J271" s="6" t="n">
+      <c r="L271" s="7" t="n">
         <v>629380</v>
       </c>
     </row>
@@ -11824,7 +13443,7 @@
           <t>SPKLU PLN POSKO CIWIDEY</t>
         </is>
       </c>
-      <c r="D272" s="8" t="inlineStr">
+      <c r="D272" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11845,12 +13464,18 @@
         </is>
       </c>
       <c r="H272" s="6" t="n">
+        <v>-7.104393</v>
+      </c>
+      <c r="I272" s="6" t="n">
+        <v>107.465925</v>
+      </c>
+      <c r="J272" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="I272" s="7" t="n">
+      <c r="K272" s="8" t="n">
         <v>238.85</v>
       </c>
-      <c r="J272" s="6" t="n">
+      <c r="L272" s="7" t="n">
         <v>624511</v>
       </c>
     </row>
@@ -11866,7 +13491,7 @@
           <t>SPKLU PLN TRANSMART TASIKMALAYA</t>
         </is>
       </c>
-      <c r="D273" s="8" t="inlineStr">
+      <c r="D273" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11887,12 +13512,18 @@
         </is>
       </c>
       <c r="H273" s="6" t="n">
+        <v>-7.317805</v>
+      </c>
+      <c r="I273" s="6" t="n">
+        <v>108.19934</v>
+      </c>
+      <c r="J273" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="I273" s="7" t="n">
+      <c r="K273" s="8" t="n">
         <v>232.36</v>
       </c>
-      <c r="J273" s="6" t="n">
+      <c r="L273" s="7" t="n">
         <v>630449</v>
       </c>
     </row>
@@ -11929,12 +13560,18 @@
         </is>
       </c>
       <c r="H274" s="6" t="n">
+        <v>-6.19819</v>
+      </c>
+      <c r="I274" s="6" t="n">
+        <v>106.97464</v>
+      </c>
+      <c r="J274" s="7" t="n">
         <v>83</v>
       </c>
-      <c r="I274" s="7" t="n">
+      <c r="K274" s="8" t="n">
         <v>230.99</v>
       </c>
-      <c r="J274" s="6" t="n">
+      <c r="L274" s="7" t="n">
         <v>615284</v>
       </c>
     </row>
@@ -11950,7 +13587,7 @@
           <t>SPKLU PLN HOTEL AMARIS</t>
         </is>
       </c>
-      <c r="D275" s="8" t="inlineStr">
+      <c r="D275" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -11971,12 +13608,18 @@
         </is>
       </c>
       <c r="H275" s="6" t="n">
+        <v>-7.3463095</v>
+      </c>
+      <c r="I275" s="6" t="n">
+        <v>108.2174077</v>
+      </c>
+      <c r="J275" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="I275" s="7" t="n">
+      <c r="K275" s="8" t="n">
         <v>226.33</v>
       </c>
-      <c r="J275" s="6" t="n">
+      <c r="L275" s="7" t="n">
         <v>614170</v>
       </c>
     </row>
@@ -11992,7 +13635,7 @@
           <t>SPKLU PLN UPDL BOGOR</t>
         </is>
       </c>
-      <c r="D276" s="8" t="inlineStr">
+      <c r="D276" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12013,12 +13656,18 @@
         </is>
       </c>
       <c r="H276" s="6" t="n">
+        <v>-6.6562553</v>
+      </c>
+      <c r="I276" s="6" t="n">
+        <v>106.8755821</v>
+      </c>
+      <c r="J276" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="I276" s="7" t="n">
+      <c r="K276" s="8" t="n">
         <v>224.45</v>
       </c>
-      <c r="J276" s="6" t="n">
+      <c r="L276" s="7" t="n">
         <v>581364</v>
       </c>
     </row>
@@ -12034,7 +13683,7 @@
           <t>SPKLU PLN ULP RENGASDENGKLOK</t>
         </is>
       </c>
-      <c r="D277" s="8" t="inlineStr">
+      <c r="D277" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12055,12 +13704,18 @@
         </is>
       </c>
       <c r="H277" s="6" t="n">
+        <v>-6.164477</v>
+      </c>
+      <c r="I277" s="6" t="n">
+        <v>107.29794</v>
+      </c>
+      <c r="J277" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="I277" s="7" t="n">
+      <c r="K277" s="8" t="n">
         <v>222.22</v>
       </c>
-      <c r="J277" s="6" t="n">
+      <c r="L277" s="7" t="n">
         <v>570118</v>
       </c>
     </row>
@@ -12076,7 +13731,7 @@
           <t>SPKLU HOTEL SUN IN PANGANDARAN</t>
         </is>
       </c>
-      <c r="D278" s="8" t="inlineStr">
+      <c r="D278" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12097,12 +13752,18 @@
         </is>
       </c>
       <c r="H278" s="6" t="n">
+        <v>-7.7011109</v>
+      </c>
+      <c r="I278" s="6" t="n">
+        <v>108.6583013</v>
+      </c>
+      <c r="J278" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="I278" s="7" t="n">
+      <c r="K278" s="8" t="n">
         <v>221.23</v>
       </c>
-      <c r="J278" s="6" t="n">
+      <c r="L278" s="7" t="n">
         <v>600307</v>
       </c>
     </row>
@@ -12118,7 +13779,7 @@
           <t>SPKLU Alun-Alun Kota Bogor</t>
         </is>
       </c>
-      <c r="D279" s="8" t="inlineStr">
+      <c r="D279" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12139,12 +13800,18 @@
         </is>
       </c>
       <c r="H279" s="6" t="n">
+        <v>-6.593879</v>
+      </c>
+      <c r="I279" s="6" t="n">
+        <v>106.791952</v>
+      </c>
+      <c r="J279" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="I279" s="7" t="n">
+      <c r="K279" s="8" t="n">
         <v>211.07</v>
       </c>
-      <c r="J279" s="6" t="n">
+      <c r="L279" s="7" t="n">
         <v>546715</v>
       </c>
     </row>
@@ -12160,7 +13827,7 @@
           <t>SPKLU PLN POSKO CIRANJANG</t>
         </is>
       </c>
-      <c r="D280" s="8" t="inlineStr">
+      <c r="D280" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12181,12 +13848,18 @@
         </is>
       </c>
       <c r="H280" s="6" t="n">
+        <v>-6.8137038</v>
+      </c>
+      <c r="I280" s="6" t="n">
+        <v>107.251689</v>
+      </c>
+      <c r="J280" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="I280" s="7" t="n">
+      <c r="K280" s="8" t="n">
         <v>194.4</v>
       </c>
-      <c r="J280" s="6" t="n">
+      <c r="L280" s="7" t="n">
         <v>508299</v>
       </c>
     </row>
@@ -12202,7 +13875,7 @@
           <t>SPKLU PLN RSUD Dr Slamet Garut</t>
         </is>
       </c>
-      <c r="D281" s="8" t="inlineStr">
+      <c r="D281" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12223,12 +13896,18 @@
         </is>
       </c>
       <c r="H281" s="6" t="n">
+        <v>-7.22043</v>
+      </c>
+      <c r="I281" s="6" t="n">
+        <v>107.8976</v>
+      </c>
+      <c r="J281" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="I281" s="7" t="n">
+      <c r="K281" s="8" t="n">
         <v>175.12</v>
       </c>
-      <c r="J281" s="6" t="n">
+      <c r="L281" s="7" t="n">
         <v>453560</v>
       </c>
     </row>
@@ -12244,7 +13923,7 @@
           <t>SPKLU (ARISTA POWER) GUDANG EV ARISTA CIKARANG (Khusus EV Milik Grup Arista)</t>
         </is>
       </c>
-      <c r="D282" s="8" t="inlineStr">
+      <c r="D282" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12265,12 +13944,18 @@
         </is>
       </c>
       <c r="H282" s="6" t="n">
+        <v>-6.2577692</v>
+      </c>
+      <c r="I282" s="6" t="n">
+        <v>107.1546401</v>
+      </c>
+      <c r="J282" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I282" s="7" t="n">
+      <c r="K282" s="8" t="n">
         <v>169.2</v>
       </c>
-      <c r="J282" s="6" t="n">
+      <c r="L282" s="7" t="n">
         <v>438255</v>
       </c>
     </row>
@@ -12286,7 +13971,7 @@
           <t>SPKLU PLN HOTEL AUGUSTA</t>
         </is>
       </c>
-      <c r="D283" s="8" t="inlineStr">
+      <c r="D283" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12307,12 +13992,18 @@
         </is>
       </c>
       <c r="H283" s="6" t="n">
+        <v>-6.96845</v>
+      </c>
+      <c r="I283" s="6" t="n">
+        <v>106.51945</v>
+      </c>
+      <c r="J283" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I283" s="7" t="n">
+      <c r="K283" s="8" t="n">
         <v>168.26</v>
       </c>
-      <c r="J283" s="6" t="n">
+      <c r="L283" s="7" t="n">
         <v>435821</v>
       </c>
     </row>
@@ -12328,7 +14019,7 @@
           <t>SPKLU PLN ULP SUMBER</t>
         </is>
       </c>
-      <c r="D284" s="8" t="inlineStr">
+      <c r="D284" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12349,12 +14040,18 @@
         </is>
       </c>
       <c r="H284" s="6" t="n">
+        <v>-6.7590768</v>
+      </c>
+      <c r="I284" s="6" t="n">
+        <v>108.4802838</v>
+      </c>
+      <c r="J284" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="I284" s="7" t="n">
+      <c r="K284" s="8" t="n">
         <v>163.39</v>
       </c>
-      <c r="J284" s="6" t="n">
+      <c r="L284" s="7" t="n">
         <v>435293</v>
       </c>
     </row>
@@ -12370,7 +14067,7 @@
           <t>SPKLU PLN ULP SUKANAGARA</t>
         </is>
       </c>
-      <c r="D285" s="8" t="inlineStr">
+      <c r="D285" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12391,12 +14088,18 @@
         </is>
       </c>
       <c r="H285" s="6" t="n">
+        <v>-7.098025</v>
+      </c>
+      <c r="I285" s="6" t="n">
+        <v>107.132026</v>
+      </c>
+      <c r="J285" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I285" s="7" t="n">
+      <c r="K285" s="8" t="n">
         <v>162.42</v>
       </c>
-      <c r="J285" s="6" t="n">
+      <c r="L285" s="7" t="n">
         <v>424653</v>
       </c>
     </row>
@@ -12412,7 +14115,7 @@
           <t>SPKLU PLN Rindu Alam Story Puncak</t>
         </is>
       </c>
-      <c r="D286" s="8" t="inlineStr">
+      <c r="D286" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12433,12 +14136,18 @@
         </is>
       </c>
       <c r="H286" s="6" t="n">
+        <v>-6.712726</v>
+      </c>
+      <c r="I286" s="6" t="n">
+        <v>107.01203</v>
+      </c>
+      <c r="J286" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="I286" s="7" t="n">
+      <c r="K286" s="8" t="n">
         <v>158.61</v>
       </c>
-      <c r="J286" s="6" t="n">
+      <c r="L286" s="7" t="n">
         <v>414760</v>
       </c>
     </row>
@@ -12454,7 +14163,7 @@
           <t>SPKLU PLN Dishub Kota Bekasi</t>
         </is>
       </c>
-      <c r="D287" s="8" t="inlineStr">
+      <c r="D287" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12475,12 +14184,18 @@
         </is>
       </c>
       <c r="H287" s="6" t="n">
+        <v>-6.230838</v>
+      </c>
+      <c r="I287" s="6" t="n">
+        <v>106.991201</v>
+      </c>
+      <c r="J287" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="I287" s="7" t="n">
+      <c r="K287" s="8" t="n">
         <v>147.07</v>
       </c>
-      <c r="J287" s="6" t="n">
+      <c r="L287" s="7" t="n">
         <v>391768</v>
       </c>
     </row>
@@ -12496,7 +14211,7 @@
           <t>SPKLU PLN 3 BISNIS CENTER KARAWANG</t>
         </is>
       </c>
-      <c r="D288" s="8" t="inlineStr">
+      <c r="D288" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12517,12 +14232,18 @@
         </is>
       </c>
       <c r="H288" s="6" t="n">
+        <v>-6.28098</v>
+      </c>
+      <c r="I288" s="6" t="n">
+        <v>107.286785</v>
+      </c>
+      <c r="J288" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="I288" s="7" t="n">
+      <c r="K288" s="8" t="n">
         <v>143.4</v>
       </c>
-      <c r="J288" s="6" t="n">
+      <c r="L288" s="7" t="n">
         <v>367878</v>
       </c>
     </row>
@@ -12538,7 +14259,7 @@
           <t>SPKLU PLN GADOG FARM</t>
         </is>
       </c>
-      <c r="D289" s="8" t="inlineStr">
+      <c r="D289" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12559,12 +14280,18 @@
         </is>
       </c>
       <c r="H289" s="6" t="n">
+        <v>-6.670561</v>
+      </c>
+      <c r="I289" s="6" t="n">
+        <v>106.891312</v>
+      </c>
+      <c r="J289" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I289" s="7" t="n">
+      <c r="K289" s="8" t="n">
         <v>143.13</v>
       </c>
-      <c r="J289" s="6" t="n">
+      <c r="L289" s="7" t="n">
         <v>370742</v>
       </c>
     </row>
@@ -12580,7 +14307,7 @@
           <t>SPKLU PLN ULP PADALARANG</t>
         </is>
       </c>
-      <c r="D290" s="8" t="inlineStr">
+      <c r="D290" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12601,12 +14328,18 @@
         </is>
       </c>
       <c r="H290" s="6" t="n">
+        <v>-6.8383096</v>
+      </c>
+      <c r="I290" s="6" t="n">
+        <v>107.4878365</v>
+      </c>
+      <c r="J290" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="I290" s="7" t="n">
+      <c r="K290" s="8" t="n">
         <v>141.46</v>
       </c>
-      <c r="J290" s="6" t="n">
+      <c r="L290" s="7" t="n">
         <v>359382</v>
       </c>
     </row>
@@ -12622,7 +14355,7 @@
           <t>SPKLU PLN ULP BANDUNG BARAT</t>
         </is>
       </c>
-      <c r="D291" s="8" t="inlineStr">
+      <c r="D291" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12643,12 +14376,18 @@
         </is>
       </c>
       <c r="H291" s="6" t="n">
+        <v>-6.908662</v>
+      </c>
+      <c r="I291" s="6" t="n">
+        <v>107.578872</v>
+      </c>
+      <c r="J291" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="I291" s="7" t="n">
+      <c r="K291" s="8" t="n">
         <v>127.08</v>
       </c>
-      <c r="J291" s="6" t="n">
+      <c r="L291" s="7" t="n">
         <v>338598</v>
       </c>
     </row>
@@ -12664,7 +14403,7 @@
           <t>SPKLU PLN RAGEMAN RESTO AND COFFEE</t>
         </is>
       </c>
-      <c r="D292" s="8" t="inlineStr">
+      <c r="D292" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12685,12 +14424,18 @@
         </is>
       </c>
       <c r="H292" s="6" t="n">
+        <v>-6.951782</v>
+      </c>
+      <c r="I292" s="6" t="n">
+        <v>108.45928</v>
+      </c>
+      <c r="J292" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="I292" s="7" t="n">
+      <c r="K292" s="8" t="n">
         <v>125.78</v>
       </c>
-      <c r="J292" s="6" t="n">
+      <c r="L292" s="7" t="n">
         <v>331998</v>
       </c>
     </row>
@@ -12706,7 +14451,7 @@
           <t>SPKLU PLN POSKO SINDANG LAUT</t>
         </is>
       </c>
-      <c r="D293" s="8" t="inlineStr">
+      <c r="D293" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12727,12 +14472,18 @@
         </is>
       </c>
       <c r="H293" s="6" t="n">
+        <v>-6.830496</v>
+      </c>
+      <c r="I293" s="6" t="n">
+        <v>108.622624</v>
+      </c>
+      <c r="J293" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I293" s="7" t="n">
+      <c r="K293" s="8" t="n">
         <v>125.26</v>
       </c>
-      <c r="J293" s="6" t="n">
+      <c r="L293" s="7" t="n">
         <v>333712</v>
       </c>
     </row>
@@ -12748,7 +14499,7 @@
           <t>SPKLU PLN ULP CIKAJANG</t>
         </is>
       </c>
-      <c r="D294" s="8" t="inlineStr">
+      <c r="D294" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12769,12 +14520,18 @@
         </is>
       </c>
       <c r="H294" s="6" t="n">
+        <v>-7.3259137</v>
+      </c>
+      <c r="I294" s="6" t="n">
+        <v>107.7948016</v>
+      </c>
+      <c r="J294" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="I294" s="7" t="n">
+      <c r="K294" s="8" t="n">
         <v>123.91</v>
       </c>
-      <c r="J294" s="6" t="n">
+      <c r="L294" s="7" t="n">
         <v>320948</v>
       </c>
     </row>
@@ -12790,7 +14547,7 @@
           <t>SPKLU PLN RM CIBIUK GARUT</t>
         </is>
       </c>
-      <c r="D295" s="8" t="inlineStr">
+      <c r="D295" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12811,12 +14568,18 @@
         </is>
       </c>
       <c r="H295" s="6" t="n">
+        <v>-7.17458</v>
+      </c>
+      <c r="I295" s="6" t="n">
+        <v>107.8911</v>
+      </c>
+      <c r="J295" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="I295" s="7" t="n">
+      <c r="K295" s="8" t="n">
         <v>123.64</v>
       </c>
-      <c r="J295" s="6" t="n">
+      <c r="L295" s="7" t="n">
         <v>320252</v>
       </c>
     </row>
@@ -12832,7 +14595,7 @@
           <t>SPKLU PLN DEALER MG SUKABUMI</t>
         </is>
       </c>
-      <c r="D296" s="9" t="inlineStr">
+      <c r="D296" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -12853,12 +14616,18 @@
         </is>
       </c>
       <c r="H296" s="6" t="n">
+        <v>-6.95598</v>
+      </c>
+      <c r="I296" s="6" t="n">
+        <v>106.90923</v>
+      </c>
+      <c r="J296" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I296" s="7" t="n">
+      <c r="K296" s="8" t="n">
         <v>117.49</v>
       </c>
-      <c r="J296" s="6" t="n">
+      <c r="L296" s="7" t="n">
         <v>304313</v>
       </c>
     </row>
@@ -12874,7 +14643,7 @@
           <t>SPKLU PLN ULP KARAWANG KOTA</t>
         </is>
       </c>
-      <c r="D297" s="8" t="inlineStr">
+      <c r="D297" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -12895,12 +14664,18 @@
         </is>
       </c>
       <c r="H297" s="6" t="n">
+        <v>-6.307692</v>
+      </c>
+      <c r="I297" s="6" t="n">
+        <v>107.292746</v>
+      </c>
+      <c r="J297" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="I297" s="7" t="n">
+      <c r="K297" s="8" t="n">
         <v>109.28</v>
       </c>
-      <c r="J297" s="6" t="n">
+      <c r="L297" s="7" t="n">
         <v>280375</v>
       </c>
     </row>
@@ -12916,7 +14691,7 @@
           <t>SPKLU PLN PDKB UP3 CIMAHI</t>
         </is>
       </c>
-      <c r="D298" s="9" t="inlineStr">
+      <c r="D298" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -12937,12 +14712,18 @@
         </is>
       </c>
       <c r="H298" s="6" t="n">
+        <v>-6.867374</v>
+      </c>
+      <c r="I298" s="6" t="n">
+        <v>107.536615</v>
+      </c>
+      <c r="J298" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I298" s="7" t="n">
+      <c r="K298" s="8" t="n">
         <v>104.27</v>
       </c>
-      <c r="J298" s="6" t="n">
+      <c r="L298" s="7" t="n">
         <v>257217</v>
       </c>
     </row>
@@ -12958,7 +14739,7 @@
           <t>SPKLU PLN ULP CILEDUG</t>
         </is>
       </c>
-      <c r="D299" s="9" t="inlineStr">
+      <c r="D299" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -12979,12 +14760,18 @@
         </is>
       </c>
       <c r="H299" s="6" t="n">
+        <v>-6.907566</v>
+      </c>
+      <c r="I299" s="6" t="n">
+        <v>108.749116</v>
+      </c>
+      <c r="J299" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I299" s="7" t="n">
+      <c r="K299" s="8" t="n">
         <v>103.11</v>
       </c>
-      <c r="J299" s="6" t="n">
+      <c r="L299" s="7" t="n">
         <v>274661</v>
       </c>
     </row>
@@ -13000,7 +14787,7 @@
           <t>SPKLU PLN PARADISO SENTUL</t>
         </is>
       </c>
-      <c r="D300" s="8" t="inlineStr">
+      <c r="D300" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -13021,12 +14808,18 @@
         </is>
       </c>
       <c r="H300" s="6" t="n">
+        <v>-6.5269121</v>
+      </c>
+      <c r="I300" s="6" t="n">
+        <v>106.8476049</v>
+      </c>
+      <c r="J300" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="I300" s="7" t="n">
+      <c r="K300" s="8" t="n">
         <v>102.28</v>
       </c>
-      <c r="J300" s="6" t="n">
+      <c r="L300" s="7" t="n">
         <v>264930</v>
       </c>
     </row>
@@ -13042,7 +14835,7 @@
           <t>SPKLU PLN HOTEL SANTIKA TASIKMALAYA</t>
         </is>
       </c>
-      <c r="D301" s="9" t="inlineStr">
+      <c r="D301" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13063,12 +14856,18 @@
         </is>
       </c>
       <c r="H301" s="6" t="n">
+        <v>-7.326161</v>
+      </c>
+      <c r="I301" s="6" t="n">
+        <v>108.217065</v>
+      </c>
+      <c r="J301" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I301" s="7" t="n">
+      <c r="K301" s="8" t="n">
         <v>101.54</v>
       </c>
-      <c r="J301" s="6" t="n">
+      <c r="L301" s="7" t="n">
         <v>275493</v>
       </c>
     </row>
@@ -13084,7 +14883,7 @@
           <t>SPKLU PLN Mall Pelayanan Publik Kabupaten Sumedang</t>
         </is>
       </c>
-      <c r="D302" s="9" t="inlineStr">
+      <c r="D302" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13105,12 +14904,18 @@
         </is>
       </c>
       <c r="H302" s="6" t="n">
+        <v>-6.860387</v>
+      </c>
+      <c r="I302" s="6" t="n">
+        <v>107.920549</v>
+      </c>
+      <c r="J302" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I302" s="7" t="n">
+      <c r="K302" s="8" t="n">
         <v>97.56999999999999</v>
       </c>
-      <c r="J302" s="6" t="n">
+      <c r="L302" s="7" t="n">
         <v>255115</v>
       </c>
     </row>
@@ -13126,7 +14931,7 @@
           <t>SPKLU PEMDA CIANJUR</t>
         </is>
       </c>
-      <c r="D303" s="8" t="inlineStr">
+      <c r="D303" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -13147,12 +14952,18 @@
         </is>
       </c>
       <c r="H303" s="6" t="n">
+        <v>-6.822256</v>
+      </c>
+      <c r="I303" s="6" t="n">
+        <v>107.138556</v>
+      </c>
+      <c r="J303" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="I303" s="7" t="n">
+      <c r="K303" s="8" t="n">
         <v>97.06999999999999</v>
       </c>
-      <c r="J303" s="6" t="n">
+      <c r="L303" s="7" t="n">
         <v>253804</v>
       </c>
     </row>
@@ -13168,7 +14979,7 @@
           <t>SPKLU PLN ULP PAGADEN</t>
         </is>
       </c>
-      <c r="D304" s="9" t="inlineStr">
+      <c r="D304" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13189,12 +15000,18 @@
         </is>
       </c>
       <c r="H304" s="6" t="n">
+        <v>-6.460969</v>
+      </c>
+      <c r="I304" s="6" t="n">
+        <v>107.810765</v>
+      </c>
+      <c r="J304" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="I304" s="7" t="n">
+      <c r="K304" s="8" t="n">
         <v>95.84999999999999</v>
       </c>
-      <c r="J304" s="6" t="n">
+      <c r="L304" s="7" t="n">
         <v>260088</v>
       </c>
     </row>
@@ -13210,7 +15027,7 @@
           <t>SPKLU PLN POSKO CICALENGKA</t>
         </is>
       </c>
-      <c r="D305" s="9" t="inlineStr">
+      <c r="D305" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13231,12 +15048,18 @@
         </is>
       </c>
       <c r="H305" s="6" t="n">
+        <v>-6.98346</v>
+      </c>
+      <c r="I305" s="6" t="n">
+        <v>107.83518</v>
+      </c>
+      <c r="J305" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I305" s="7" t="n">
+      <c r="K305" s="8" t="n">
         <v>95.14</v>
       </c>
-      <c r="J305" s="6" t="n">
+      <c r="L305" s="7" t="n">
         <v>248791</v>
       </c>
     </row>
@@ -13252,7 +15075,7 @@
           <t>SPKLU PLN HOTEL ARNAWA PANGANDARAN</t>
         </is>
       </c>
-      <c r="D306" s="9" t="inlineStr">
+      <c r="D306" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13273,12 +15096,18 @@
         </is>
       </c>
       <c r="H306" s="6" t="n">
+        <v>-7.693102</v>
+      </c>
+      <c r="I306" s="6" t="n">
+        <v>108.653557</v>
+      </c>
+      <c r="J306" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I306" s="7" t="n">
+      <c r="K306" s="8" t="n">
         <v>88.17</v>
       </c>
-      <c r="J306" s="6" t="n">
+      <c r="L306" s="7" t="n">
         <v>239245</v>
       </c>
     </row>
@@ -13294,7 +15123,7 @@
           <t>SPKLU PLN TIRTAGANGGA HOTEL GARUT</t>
         </is>
       </c>
-      <c r="D307" s="9" t="inlineStr">
+      <c r="D307" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13315,12 +15144,18 @@
         </is>
       </c>
       <c r="H307" s="6" t="n">
+        <v>-7.17816</v>
+      </c>
+      <c r="I307" s="6" t="n">
+        <v>107.8713</v>
+      </c>
+      <c r="J307" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I307" s="7" t="n">
+      <c r="K307" s="8" t="n">
         <v>87.98999999999999</v>
       </c>
-      <c r="J307" s="6" t="n">
+      <c r="L307" s="7" t="n">
         <v>227909</v>
       </c>
     </row>
@@ -13336,7 +15171,7 @@
           <t>SPKLU PLN Posko Cisarua</t>
         </is>
       </c>
-      <c r="D308" s="9" t="inlineStr">
+      <c r="D308" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13357,12 +15192,18 @@
         </is>
       </c>
       <c r="H308" s="6" t="n">
+        <v>-6.7977</v>
+      </c>
+      <c r="I308" s="6" t="n">
+        <v>107.574637</v>
+      </c>
+      <c r="J308" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I308" s="7" t="n">
+      <c r="K308" s="8" t="n">
         <v>86.65000000000001</v>
       </c>
-      <c r="J308" s="6" t="n">
+      <c r="L308" s="7" t="n">
         <v>226574</v>
       </c>
     </row>
@@ -13378,7 +15219,7 @@
           <t>SPKLU POLRES KARAWANG</t>
         </is>
       </c>
-      <c r="D309" s="9" t="inlineStr">
+      <c r="D309" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13399,12 +15240,18 @@
         </is>
       </c>
       <c r="H309" s="6" t="n">
+        <v>-6.332562</v>
+      </c>
+      <c r="I309" s="6" t="n">
+        <v>107.333055</v>
+      </c>
+      <c r="J309" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I309" s="7" t="n">
+      <c r="K309" s="8" t="n">
         <v>82.11</v>
       </c>
-      <c r="J309" s="6" t="n">
+      <c r="L309" s="7" t="n">
         <v>210635</v>
       </c>
     </row>
@@ -13420,7 +15267,7 @@
           <t>SPKLU PLN ULP CILILIN</t>
         </is>
       </c>
-      <c r="D310" s="8" t="inlineStr">
+      <c r="D310" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -13441,12 +15288,18 @@
         </is>
       </c>
       <c r="H310" s="6" t="n">
+        <v>-6.947899</v>
+      </c>
+      <c r="I310" s="6" t="n">
+        <v>107.46704</v>
+      </c>
+      <c r="J310" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I310" s="7" t="n">
+      <c r="K310" s="8" t="n">
         <v>80.62</v>
       </c>
-      <c r="J310" s="6" t="n">
+      <c r="L310" s="7" t="n">
         <v>204852</v>
       </c>
     </row>
@@ -13462,7 +15315,7 @@
           <t>SPKLU PLN DISHUB KAB. CIREBON</t>
         </is>
       </c>
-      <c r="D311" s="8" t="inlineStr">
+      <c r="D311" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -13483,12 +15336,18 @@
         </is>
       </c>
       <c r="H311" s="6" t="n">
+        <v>-6.758782</v>
+      </c>
+      <c r="I311" s="6" t="n">
+        <v>108.481621</v>
+      </c>
+      <c r="J311" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I311" s="7" t="n">
+      <c r="K311" s="8" t="n">
         <v>77.59</v>
       </c>
-      <c r="J311" s="6" t="n">
+      <c r="L311" s="7" t="n">
         <v>206717</v>
       </c>
     </row>
@@ -13504,7 +15363,7 @@
           <t>SPKLU PLN Hotel Grand Cahaya Pangandaran</t>
         </is>
       </c>
-      <c r="D312" s="9" t="inlineStr">
+      <c r="D312" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13525,12 +15384,18 @@
         </is>
       </c>
       <c r="H312" s="6" t="n">
+        <v>-7.695052</v>
+      </c>
+      <c r="I312" s="6" t="n">
+        <v>108.655097</v>
+      </c>
+      <c r="J312" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I312" s="7" t="n">
+      <c r="K312" s="8" t="n">
         <v>73.64</v>
       </c>
-      <c r="J312" s="6" t="n">
+      <c r="L312" s="7" t="n">
         <v>199807</v>
       </c>
     </row>
@@ -13546,7 +15411,7 @@
           <t>SPKLU PLN POSKO WARUNG KONDANG</t>
         </is>
       </c>
-      <c r="D313" s="9" t="inlineStr">
+      <c r="D313" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13567,12 +15432,18 @@
         </is>
       </c>
       <c r="H313" s="6" t="n">
+        <v>-6.870025</v>
+      </c>
+      <c r="I313" s="6" t="n">
+        <v>107.098276</v>
+      </c>
+      <c r="J313" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I313" s="7" t="n">
+      <c r="K313" s="8" t="n">
         <v>71.88</v>
       </c>
-      <c r="J313" s="6" t="n">
+      <c r="L313" s="7" t="n">
         <v>187956</v>
       </c>
     </row>
@@ -13588,7 +15459,7 @@
           <t>SPKLU PLN OCEAN VIEW</t>
         </is>
       </c>
-      <c r="D314" s="9" t="inlineStr">
+      <c r="D314" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13609,12 +15480,18 @@
         </is>
       </c>
       <c r="H314" s="6" t="n">
+        <v>-7.466948</v>
+      </c>
+      <c r="I314" s="6" t="n">
+        <v>107.169861</v>
+      </c>
+      <c r="J314" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I314" s="7" t="n">
+      <c r="K314" s="8" t="n">
         <v>61.68</v>
       </c>
-      <c r="J314" s="6" t="n">
+      <c r="L314" s="7" t="n">
         <v>161283</v>
       </c>
     </row>
@@ -13630,7 +15507,7 @@
           <t>SPKLU PLN ULP RAJAMANDALA</t>
         </is>
       </c>
-      <c r="D315" s="8" t="inlineStr">
+      <c r="D315" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -13651,12 +15528,18 @@
         </is>
       </c>
       <c r="H315" s="6" t="n">
+        <v>-6.833078</v>
+      </c>
+      <c r="I315" s="6" t="n">
+        <v>107.346798</v>
+      </c>
+      <c r="J315" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="I315" s="7" t="n">
+      <c r="K315" s="8" t="n">
         <v>60.43</v>
       </c>
-      <c r="J315" s="6" t="n">
+      <c r="L315" s="7" t="n">
         <v>153500</v>
       </c>
     </row>
@@ -13672,7 +15555,7 @@
           <t>SPKLU PLN MESJID ENDAN</t>
         </is>
       </c>
-      <c r="D316" s="8" t="inlineStr">
+      <c r="D316" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
@@ -13693,12 +15576,18 @@
         </is>
       </c>
       <c r="H316" s="6" t="n">
+        <v>-6.699598</v>
+      </c>
+      <c r="I316" s="6" t="n">
+        <v>107.473717</v>
+      </c>
+      <c r="J316" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I316" s="7" t="n">
+      <c r="K316" s="8" t="n">
         <v>59.78</v>
       </c>
-      <c r="J316" s="6" t="n">
+      <c r="L316" s="7" t="n">
         <v>151855</v>
       </c>
     </row>
@@ -13714,7 +15603,7 @@
           <t>SPKLU PLN POSKO CIKIJING</t>
         </is>
       </c>
-      <c r="D317" s="9" t="inlineStr">
+      <c r="D317" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13735,12 +15624,18 @@
         </is>
       </c>
       <c r="H317" s="6" t="n">
+        <v>-7.020685</v>
+      </c>
+      <c r="I317" s="6" t="n">
+        <v>108.391911</v>
+      </c>
+      <c r="J317" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I317" s="7" t="n">
+      <c r="K317" s="8" t="n">
         <v>55.23</v>
       </c>
-      <c r="J317" s="6" t="n">
+      <c r="L317" s="7" t="n">
         <v>145779</v>
       </c>
     </row>
@@ -13756,7 +15651,7 @@
           <t>SPKLU PLN POSKO CIPARAY</t>
         </is>
       </c>
-      <c r="D318" s="9" t="inlineStr">
+      <c r="D318" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13777,12 +15672,18 @@
         </is>
       </c>
       <c r="H318" s="6" t="n">
+        <v>-7.035193</v>
+      </c>
+      <c r="I318" s="6" t="n">
+        <v>107.712</v>
+      </c>
+      <c r="J318" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="I318" s="7" t="n">
+      <c r="K318" s="8" t="n">
         <v>44.27</v>
       </c>
-      <c r="J318" s="6" t="n">
+      <c r="L318" s="7" t="n">
         <v>115759</v>
       </c>
     </row>
@@ -13798,7 +15699,7 @@
           <t>SPKLU PLN ULP TANGGEUNG</t>
         </is>
       </c>
-      <c r="D319" s="9" t="inlineStr">
+      <c r="D319" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13819,12 +15720,18 @@
         </is>
       </c>
       <c r="H319" s="6" t="n">
+        <v>-7.2676151</v>
+      </c>
+      <c r="I319" s="6" t="n">
+        <v>107.1200746</v>
+      </c>
+      <c r="J319" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I319" s="7" t="n">
+      <c r="K319" s="8" t="n">
         <v>42.31</v>
       </c>
-      <c r="J319" s="6" t="n">
+      <c r="L319" s="7" t="n">
         <v>110584</v>
       </c>
     </row>
@@ -13840,7 +15747,7 @@
           <t>SPKLU PLN POSKO CIBEBER</t>
         </is>
       </c>
-      <c r="D320" s="9" t="inlineStr">
+      <c r="D320" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13861,12 +15768,18 @@
         </is>
       </c>
       <c r="H320" s="6" t="n">
+        <v>-6.936976</v>
+      </c>
+      <c r="I320" s="6" t="n">
+        <v>107.12325</v>
+      </c>
+      <c r="J320" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I320" s="7" t="n">
+      <c r="K320" s="8" t="n">
         <v>39.71</v>
       </c>
-      <c r="J320" s="6" t="n">
+      <c r="L320" s="7" t="n">
         <v>103838</v>
       </c>
     </row>
@@ -13882,7 +15795,7 @@
           <t>SPKLU PLN ULP PLERED</t>
         </is>
       </c>
-      <c r="D321" s="9" t="inlineStr">
+      <c r="D321" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13903,12 +15816,18 @@
         </is>
       </c>
       <c r="H321" s="6" t="n">
+        <v>-6.638197</v>
+      </c>
+      <c r="I321" s="6" t="n">
+        <v>107.406718</v>
+      </c>
+      <c r="J321" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I321" s="7" t="n">
+      <c r="K321" s="8" t="n">
         <v>34.66</v>
       </c>
-      <c r="J321" s="6" t="n">
+      <c r="L321" s="7" t="n">
         <v>88037</v>
       </c>
     </row>
@@ -13924,7 +15843,7 @@
           <t>SPKLU PLN ISTANA PRESIDEN CIPANAS (Khusus Internal Istana Presiden)</t>
         </is>
       </c>
-      <c r="D322" s="9" t="inlineStr">
+      <c r="D322" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13945,12 +15864,18 @@
         </is>
       </c>
       <c r="H322" s="6" t="n">
+        <v>-6.732474</v>
+      </c>
+      <c r="I322" s="6" t="n">
+        <v>107.040642</v>
+      </c>
+      <c r="J322" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I322" s="7" t="n">
+      <c r="K322" s="8" t="n">
         <v>33.87</v>
       </c>
-      <c r="J322" s="6" t="n">
+      <c r="L322" s="7" t="n">
         <v>88569</v>
       </c>
     </row>
@@ -13966,7 +15891,7 @@
           <t>SPKLU PLN MASJID BAITUL MUMININ CAMPAKA</t>
         </is>
       </c>
-      <c r="D323" s="9" t="inlineStr">
+      <c r="D323" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -13987,12 +15912,18 @@
         </is>
       </c>
       <c r="H323" s="6" t="n">
+        <v>-7.016566</v>
+      </c>
+      <c r="I323" s="6" t="n">
+        <v>107.138514</v>
+      </c>
+      <c r="J323" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I323" s="7" t="n">
+      <c r="K323" s="8" t="n">
         <v>26.55</v>
       </c>
-      <c r="J323" s="6" t="n">
+      <c r="L323" s="7" t="n">
         <v>69427</v>
       </c>
     </row>
@@ -14008,7 +15939,7 @@
           <t>SPKLU PLN RM SAMOLO</t>
         </is>
       </c>
-      <c r="D324" s="9" t="inlineStr">
+      <c r="D324" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -14029,12 +15960,18 @@
         </is>
       </c>
       <c r="H324" s="6" t="n">
+        <v>-6.799374</v>
+      </c>
+      <c r="I324" s="6" t="n">
+        <v>107.200251</v>
+      </c>
+      <c r="J324" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I324" s="7" t="n">
+      <c r="K324" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="J324" s="6" t="n">
+      <c r="L324" s="7" t="n">
         <v>56745</v>
       </c>
     </row>
@@ -14050,7 +15987,7 @@
           <t>SPKLU CIANJUR ASRI</t>
         </is>
       </c>
-      <c r="D325" s="9" t="inlineStr">
+      <c r="D325" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -14071,12 +16008,18 @@
         </is>
       </c>
       <c r="H325" s="6" t="n">
+        <v>-6.848277</v>
+      </c>
+      <c r="I325" s="6" t="n">
+        <v>107.127251</v>
+      </c>
+      <c r="J325" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I325" s="7" t="n">
+      <c r="K325" s="8" t="n">
         <v>20.98</v>
       </c>
-      <c r="J325" s="6" t="n">
+      <c r="L325" s="7" t="n">
         <v>54883</v>
       </c>
     </row>
@@ -14092,7 +16035,7 @@
           <t>SPKLU POLDA JABAR</t>
         </is>
       </c>
-      <c r="D326" s="9" t="inlineStr">
+      <c r="D326" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -14113,12 +16056,18 @@
         </is>
       </c>
       <c r="H326" s="6" t="n">
+        <v>-6.936338</v>
+      </c>
+      <c r="I326" s="6" t="n">
+        <v>107.704642</v>
+      </c>
+      <c r="J326" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I326" s="7" t="n">
+      <c r="K326" s="8" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="J326" s="6" t="n">
+      <c r="L326" s="7" t="n">
         <v>22070</v>
       </c>
     </row>
@@ -14134,7 +16083,7 @@
           <t>SPKLU ALUN-ALUN SINDANGBARANG</t>
         </is>
       </c>
-      <c r="D327" s="9" t="inlineStr">
+      <c r="D327" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -14155,12 +16104,18 @@
         </is>
       </c>
       <c r="H327" s="6" t="n">
+        <v>-7.451419</v>
+      </c>
+      <c r="I327" s="6" t="n">
+        <v>107.134878</v>
+      </c>
+      <c r="J327" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I327" s="7" t="n">
+      <c r="K327" s="8" t="n">
         <v>7.87</v>
       </c>
-      <c r="J327" s="6" t="n">
+      <c r="L327" s="7" t="n">
         <v>20598</v>
       </c>
     </row>
@@ -14176,7 +16131,7 @@
           <t>SPKLU PLN Posko Citatah</t>
         </is>
       </c>
-      <c r="D328" s="9" t="inlineStr">
+      <c r="D328" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -14197,12 +16152,18 @@
         </is>
       </c>
       <c r="H328" s="6" t="n">
+        <v>-6.83452</v>
+      </c>
+      <c r="I328" s="6" t="n">
+        <v>107.426411</v>
+      </c>
+      <c r="J328" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I328" s="7" t="n">
+      <c r="K328" s="8" t="n">
         <v>4.69</v>
       </c>
-      <c r="J328" s="6" t="n">
+      <c r="L328" s="7" t="n">
         <v>12265</v>
       </c>
     </row>
@@ -14218,7 +16179,7 @@
           <t>SPKLU PLN ULP BALEENDAH</t>
         </is>
       </c>
-      <c r="D329" s="9" t="inlineStr">
+      <c r="D329" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -14239,12 +16200,18 @@
         </is>
       </c>
       <c r="H329" s="6" t="n">
+        <v>-7.006223</v>
+      </c>
+      <c r="I329" s="6" t="n">
+        <v>107.625739</v>
+      </c>
+      <c r="J329" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I329" s="7" t="n">
+      <c r="K329" s="8" t="n">
         <v>4.38</v>
       </c>
-      <c r="J329" s="6" t="n">
+      <c r="L329" s="7" t="n">
         <v>11454</v>
       </c>
     </row>
@@ -14260,7 +16227,7 @@
           <t>SPKLU PLN POSKO CIMALAKA</t>
         </is>
       </c>
-      <c r="D330" s="9" t="inlineStr">
+      <c r="D330" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -14281,12 +16248,18 @@
         </is>
       </c>
       <c r="H330" s="6" t="n">
+        <v>-6.815006</v>
+      </c>
+      <c r="I330" s="6" t="n">
+        <v>107.959884</v>
+      </c>
+      <c r="J330" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I330" s="7" t="n">
+      <c r="K330" s="8" t="n">
         <v>3.03</v>
       </c>
-      <c r="J330" s="6" t="n">
+      <c r="L330" s="7" t="n">
         <v>7926</v>
       </c>
     </row>
@@ -14302,7 +16275,7 @@
           <t>SPKLU PLN Posko Cugenang</t>
         </is>
       </c>
-      <c r="D331" s="9" t="inlineStr">
+      <c r="D331" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -14323,12 +16296,18 @@
         </is>
       </c>
       <c r="H331" s="6" t="n">
+        <v>-6.799131</v>
+      </c>
+      <c r="I331" s="6" t="n">
+        <v>107.0789</v>
+      </c>
+      <c r="J331" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I331" s="7" t="n">
+      <c r="K331" s="8" t="n">
         <v>2.57</v>
       </c>
-      <c r="J331" s="6" t="n">
+      <c r="L331" s="7" t="n">
         <v>6722</v>
       </c>
     </row>
@@ -14344,7 +16323,7 @@
           <t>SPKLU  PLN Posko Cikalong Wetan</t>
         </is>
       </c>
-      <c r="D332" s="9" t="inlineStr">
+      <c r="D332" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -14365,12 +16344,18 @@
         </is>
       </c>
       <c r="H332" s="6" t="n">
+        <v>-6.740749</v>
+      </c>
+      <c r="I332" s="6" t="n">
+        <v>107.440882</v>
+      </c>
+      <c r="J332" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I332" s="7" t="n">
+      <c r="K332" s="8" t="n">
         <v>2.39</v>
       </c>
-      <c r="J332" s="6" t="n">
+      <c r="L332" s="7" t="n">
         <v>6074</v>
       </c>
     </row>
@@ -14386,7 +16371,7 @@
           <t>SPKLU PLN ULP PURWAKARTA KOTA</t>
         </is>
       </c>
-      <c r="D333" s="9" t="inlineStr">
+      <c r="D333" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -14407,12 +16392,18 @@
         </is>
       </c>
       <c r="H333" s="6" t="n">
+        <v>-6.554661</v>
+      </c>
+      <c r="I333" s="6" t="n">
+        <v>107.445698</v>
+      </c>
+      <c r="J333" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I333" s="7" t="n">
+      <c r="K333" s="8" t="n">
         <v>0.21</v>
       </c>
-      <c r="J333" s="6" t="n">
+      <c r="L333" s="7" t="n">
         <v>539</v>
       </c>
     </row>
@@ -14428,7 +16419,7 @@
           <t>SPKLU PLN ADVENTURE CAMP CIJERUK</t>
         </is>
       </c>
-      <c r="D334" s="9" t="inlineStr">
+      <c r="D334" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
@@ -14449,12 +16440,18 @@
         </is>
       </c>
       <c r="H334" s="6" t="n">
+        <v>-6.676014</v>
+      </c>
+      <c r="I334" s="6" t="n">
+        <v>106.784682</v>
+      </c>
+      <c r="J334" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I334" s="7" t="n">
+      <c r="K334" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="J334" s="6" t="n">
+      <c r="L334" s="7" t="n">
         <v>288</v>
       </c>
     </row>
@@ -14526,16 +16523,16 @@
           <t>Kantor / Unit Layanan PLN</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="7" t="n">
         <v>132</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="8" t="n">
         <v>695757</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>31966</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="8" t="n">
         <v>5270.9</v>
       </c>
     </row>
@@ -14545,16 +16542,16 @@
           <t>Rest Area Tol</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>672260.8</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>28405</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <v>19207.5</v>
       </c>
     </row>
@@ -14564,16 +16561,16 @@
           <t>Dealer / Showroom Mobil</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>225459</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>9464</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="8" t="n">
         <v>17343</v>
       </c>
     </row>
@@ -14583,16 +16580,16 @@
           <t>Perumahan / Township</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>177014.3</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>8016</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="8" t="n">
         <v>9316.5</v>
       </c>
     </row>
@@ -14602,16 +16599,16 @@
           <t>Mall / Retail / Supermarket</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>164301</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>7732</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="8" t="n">
         <v>7823.9</v>
       </c>
     </row>
@@ -14621,16 +16618,16 @@
           <t>Publik / Pemerintah / Transportasi</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <v>136482.8</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>6087</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="8" t="n">
         <v>5686.8</v>
       </c>
     </row>
@@ -14640,16 +16637,16 @@
           <t>F&amp;B / Kafe / Leisure Retail</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <v>85927</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>3931</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="8" t="n">
         <v>4773.7</v>
       </c>
     </row>
@@ -14659,16 +16656,16 @@
           <t>Hotel / Hospitality</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>56045</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>2828</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="8" t="n">
         <v>1401.1</v>
       </c>
     </row>
@@ -14678,16 +16675,16 @@
           <t>Lainnya / Campuran</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="8" t="n">
         <v>27503.1</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>1325</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="8" t="n">
         <v>4583.9</v>
       </c>
     </row>
@@ -14697,16 +16694,16 @@
           <t>Rumah Sakit / Kesehatan</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="8" t="n">
         <v>6703.1</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="7" t="n">
         <v>486</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="8" t="n">
         <v>837.9</v>
       </c>
     </row>
@@ -14716,16 +16713,16 @@
           <t>Perkantoran / Gedung Komersial</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="8" t="n">
         <v>6381.9</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <v>387</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="8" t="n">
         <v>2127.3</v>
       </c>
     </row>
@@ -14735,16 +16732,16 @@
           <t>Wisata / Leisure</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="8" t="n">
         <v>5713.2</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="7" t="n">
         <v>393</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="8" t="n">
         <v>571.3</v>
       </c>
     </row>
@@ -14810,45 +16807,45 @@
           <t>Hijau (Utilisasi Tinggi &gt;50 trx)</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="7" t="n">
         <v>190</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="8" t="n">
         <v>2215533.7</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>97713</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Kuning (Utilisasi Sedang 11-50 trx)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>42394.8</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>3112</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Merah (Utilisasi Rendah &lt;10 trx)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>1619.9</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>195</v>
       </c>
     </row>
